--- a/data/gene_neighbourhood/tables/gene_maps_halobacteria_5kb.xlsx
+++ b/data/gene_neighbourhood/tables/gene_maps_halobacteria_5kb.xlsx
@@ -8952,7 +8952,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P146"/>
+  <dimension ref="A1:P150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10915,12 +10915,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Haladaptatus paucihalophilus</t>
+          <t>Halegenticoccus tardaugens</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>GCF_000376445.1</t>
+          <t>GCF_004116405.1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -10936,14 +10936,14 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>NZ_AQXI01000001.1</t>
+          <t>NZ_SDIC01000004.1</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>32337</v>
+        <v>271224</v>
       </c>
       <c r="I29" t="n">
-        <v>33278</v>
+        <v>271868</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -10952,26 +10952,26 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>NZ_AQXI01000001.1_42</t>
+          <t>NZ_SDIC01000004.1_283</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>313</v>
+        <v>214</v>
       </c>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
-          <t>B208_RS0100215</t>
+          <t>C3L37_RS12300</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>WP_007978260.1</t>
+          <t>WP_129114908.1</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>archaeosortase A</t>
+          <t>hypothetical protein</t>
         </is>
       </c>
     </row>
@@ -10981,12 +10981,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Haladaptatus paucihalophilus</t>
+          <t>Halegenticoccus tardaugens</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>GCF_000376445.1</t>
+          <t>GCF_004116405.1</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -11002,46 +11002,46 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>NZ_AQXI01000001.1</t>
+          <t>NZ_SDIC01000004.1</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>31294</v>
+        <v>271904</v>
       </c>
       <c r="I30" t="n">
-        <v>32076</v>
+        <v>272188</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>NZ_AQXI01000001.1_41</t>
+          <t>NZ_SDIC01000004.1_284</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>260</v>
+        <v>94</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>HTH_24 + MarR_2 + MarR + HTH_IclR</t>
+          <t>Ribosomal_L44</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>B208_RS0100210</t>
+          <t>C3L37_RS12305</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>WP_007978258.1</t>
+          <t>WP_129114909.1</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>DUF7839 domain-containing protein</t>
+          <t>50S ribosomal protein L44e</t>
         </is>
       </c>
     </row>
@@ -11051,12 +11051,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Haladaptatus paucihalophilus</t>
+          <t>Halegenticoccus tardaugens</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>GCF_000376445.1</t>
+          <t>GCF_004116405.1</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -11072,14 +11072,14 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>NZ_AQXI01000001.1</t>
+          <t>NZ_SDIC01000004.1</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>30701</v>
+        <v>272193</v>
       </c>
       <c r="I31" t="n">
-        <v>31267</v>
+        <v>272366</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -11088,30 +11088,30 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>NZ_AQXI01000001.1_40</t>
+          <t>NZ_SDIC01000004.1_285</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>188</v>
+        <v>57</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>DnaJ</t>
+          <t>Ribosomal_S27e</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>B208_RS0100205</t>
+          <t>C3L37_RS12310</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>WP_007978256.1</t>
+          <t>WP_129114910.1</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>J domain-containing protein</t>
+          <t>30S ribosomal protein S27e</t>
         </is>
       </c>
     </row>
@@ -11121,12 +11121,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Haladaptatus paucihalophilus</t>
+          <t>Halegenticoccus tardaugens</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>GCF_000376445.1</t>
+          <t>GCF_004116405.1</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -11142,42 +11142,46 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>NZ_AQXI01000001.1</t>
+          <t>NZ_SDIC01000004.1</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>29915</v>
+        <v>272382</v>
       </c>
       <c r="I32" t="n">
-        <v>30442</v>
+        <v>273182</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>NZ_AQXI01000001.1_39</t>
+          <t>NZ_SDIC01000004.1_286</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>175</v>
-      </c>
-      <c r="M32" t="inlineStr"/>
+        <v>266</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>S1 + EIF_2_alpha</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>B208_RS0100200</t>
+          <t>C3L37_RS12315</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>WP_007978253.1</t>
+          <t>WP_129114911.1</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>DUF7344 domain-containing protein</t>
+          <t>translation initiation factor IF-2 subunit alpha</t>
         </is>
       </c>
     </row>
@@ -11187,12 +11191,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Haladaptatus paucihalophilus</t>
+          <t>Halegenticoccus tardaugens</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>GCF_000376445.1</t>
+          <t>GCF_004116405.1</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -11208,14 +11212,14 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>NZ_AQXI01000001.1</t>
+          <t>NZ_SDIC01000004.1</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>29135</v>
+        <v>273187</v>
       </c>
       <c r="I33" t="n">
-        <v>29893</v>
+        <v>273372</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -11224,30 +11228,30 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>NZ_AQXI01000001.1_38</t>
+          <t>NZ_SDIC01000004.1_287</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>252</v>
+        <v>61</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>PAC2</t>
+          <t>Nop10p</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>B208_RS0100195</t>
+          <t>C3L37_RS12320</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>WP_007978252.1</t>
+          <t>WP_129114912.1</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>proteasome assembly chaperone family protein</t>
+          <t>RNA-protein complex protein Nop10</t>
         </is>
       </c>
     </row>
@@ -11257,12 +11261,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Haladaptatus paucihalophilus</t>
+          <t>Halegenticoccus tardaugens</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>GCF_000376445.1</t>
+          <t>GCF_004116405.1</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -11278,14 +11282,14 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>NZ_AQXI01000001.1</t>
+          <t>NZ_SDIC01000004.1</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>28947</v>
+        <v>273460</v>
       </c>
       <c r="I34" t="n">
-        <v>29129</v>
+        <v>274215</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -11294,30 +11298,30 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>NZ_AQXI01000001.1_37</t>
+          <t>NZ_SDIC01000004.1_288</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>60</v>
+        <v>251</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Nop10p</t>
+          <t>PAC2</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>B208_RS0100190</t>
+          <t>C3L37_RS12325</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>WP_007978250.1</t>
+          <t>WP_129114913.1</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>RNA-protein complex protein Nop10</t>
+          <t>proteasome assembly chaperone family protein</t>
         </is>
       </c>
     </row>
@@ -11327,12 +11331,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Haladaptatus paucihalophilus</t>
+          <t>Halegenticoccus tardaugens</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>GCF_000376445.1</t>
+          <t>GCF_004116405.1</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -11348,14 +11352,14 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>NZ_AQXI01000001.1</t>
+          <t>NZ_SDIC01000004.1</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>28150</v>
+        <v>274326</v>
       </c>
       <c r="I35" t="n">
-        <v>28950</v>
+        <v>274496</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -11364,30 +11368,26 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>NZ_AQXI01000001.1_36</t>
+          <t>NZ_SDIC01000004.1_289</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>266</v>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>S1 + EIF_2_alpha</t>
-        </is>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
-          <t>B208_RS0100185</t>
+          <t>C3L37_RS24370</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>WP_007978248.1</t>
+          <t>WP_164974745.1</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>translation initiation factor IF-2 subunit alpha</t>
+          <t>hypothetical protein</t>
         </is>
       </c>
     </row>
@@ -11397,12 +11397,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Haladaptatus paucihalophilus</t>
+          <t>Halegenticoccus tardaugens</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>GCF_000376445.1</t>
+          <t>GCF_004116405.1</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -11418,46 +11418,46 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>NZ_AQXI01000001.1</t>
+          <t>NZ_SDIC01000004.1</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>27980</v>
+        <v>274595</v>
       </c>
       <c r="I36" t="n">
-        <v>28153</v>
+        <v>275212</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>NZ_AQXI01000001.1_35</t>
+          <t>NZ_SDIC01000004.1_290</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>57</v>
+        <v>205</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Ribosomal_S27e</t>
+          <t>DUF420</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>B208_RS0100180</t>
+          <t>C3L37_RS12330</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>WP_007978247.1</t>
+          <t>WP_129114914.1</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>30S ribosomal protein S27e</t>
+          <t>DUF420 domain-containing protein</t>
         </is>
       </c>
     </row>
@@ -11467,12 +11467,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Haladaptatus paucihalophilus</t>
+          <t>Halegenticoccus tardaugens</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>GCF_000376445.1</t>
+          <t>GCF_004116405.1</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -11488,46 +11488,46 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>NZ_AQXI01000001.1</t>
+          <t>NZ_SDIC01000004.1</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>27790</v>
+        <v>275382</v>
       </c>
       <c r="I37" t="n">
-        <v>27975</v>
+        <v>276434</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>NZ_AQXI01000001.1_34</t>
+          <t>NZ_SDIC01000004.1_291</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>61</v>
+        <v>350</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Ribosomal_L44</t>
+          <t>Fe-ADH + Fe-ADH_2 + DHQ_synthase</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>B208_RS0100175</t>
+          <t>C3L37_RS12335</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>WP_007978245.1</t>
+          <t>WP_129114915.1</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>50S ribosomal protein L44e</t>
+          <t>NAD(P)-dependent glycerol-1-phosphate dehydrogenase</t>
         </is>
       </c>
     </row>
@@ -11537,12 +11537,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Haladaptatus paucihalophilus</t>
+          <t>Halegenticoccus tardaugens</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>GCF_000376445.1</t>
+          <t>GCF_004116405.1</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -11558,42 +11558,46 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>NZ_AQXI01000001.1</t>
+          <t>NZ_SDIC01000004.1</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>26622</v>
+        <v>276759</v>
       </c>
       <c r="I38" t="n">
-        <v>27524</v>
+        <v>277637</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>NZ_AQXI01000001.1_33</t>
+          <t>NZ_SDIC01000004.1_292</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>300</v>
-      </c>
-      <c r="M38" t="inlineStr"/>
+        <v>292</v>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>DUF900</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>B208_RS0100170</t>
+          <t>C3L37_RS12340</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>WP_049805627.1</t>
+          <t>WP_129115263.1</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>hypothetical protein</t>
+          <t>alpha/beta hydrolase</t>
         </is>
       </c>
     </row>
@@ -11603,12 +11607,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Haladaptatus paucihalophilus</t>
+          <t>Halegenticoccus tardaugens</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>GCF_000376445.1</t>
+          <t>GCF_004116405.1</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -11624,14 +11628,14 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>NZ_AQXI01000001.1</t>
+          <t>NZ_SDIC01000004.1</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>25711</v>
+        <v>277692</v>
       </c>
       <c r="I39" t="n">
-        <v>26610</v>
+        <v>278429</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -11640,30 +11644,30 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>NZ_AQXI01000001.1_32</t>
+          <t>NZ_SDIC01000004.1_293</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>299</v>
+        <v>245</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>DUF900</t>
+          <t>LysE</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>B208_RS0100165</t>
+          <t>C3L37_RS12345</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>WP_007978241.1</t>
+          <t>WP_129115264.1</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>alpha/beta hydrolase</t>
+          <t>LysE family translocator</t>
         </is>
       </c>
     </row>
@@ -11673,12 +11677,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Haladaptatus paucihalophilus</t>
+          <t>Halegenticoccus tardaugens</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>GCF_000376445.1</t>
+          <t>GCF_004116405.1</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -11694,14 +11698,14 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>NZ_AQXI01000001.1</t>
+          <t>NZ_SDIC01000004.1</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>25349</v>
+        <v>278512</v>
       </c>
       <c r="I40" t="n">
-        <v>25618</v>
+        <v>279186</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -11710,26 +11714,30 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>NZ_AQXI01000001.1_31</t>
+          <t>NZ_SDIC01000004.1_294</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>89</v>
-      </c>
-      <c r="M40" t="inlineStr"/>
+        <v>224</v>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Fe_dep_repress + MarR_2 + MarR + HTH_IclR + Fe_dep_repr_C + FeoA</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>B208_RS0100160</t>
+          <t>C3L37_RS12350</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>WP_007978239.1</t>
+          <t>WP_129114916.1</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>HAH_0734 family protein</t>
+          <t>metal-dependent transcriptional regulator</t>
         </is>
       </c>
     </row>
@@ -11739,12 +11747,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Haladaptatus paucihalophilus</t>
+          <t>Halegenticoccus tardaugens</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>GCF_000376445.1</t>
+          <t>GCF_004116405.1</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -11760,14 +11768,14 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>NZ_AQXI01000001.1</t>
+          <t>NZ_SDIC01000004.1</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>23821</v>
+        <v>279308</v>
       </c>
       <c r="I41" t="n">
-        <v>24987</v>
+        <v>280501</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -11776,30 +11784,30 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>NZ_AQXI01000001.1_30</t>
+          <t>NZ_SDIC01000004.1_295</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>388</v>
+        <v>397</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Thiolase_N + ketoacyl-synt + Thiolase_C_1 + Thiolase_C</t>
+          <t>PALP</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>B208_RS0100155</t>
+          <t>C3L37_RS12355</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>WP_007978238.1</t>
+          <t>WP_129114917.1</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>thiolase domain-containing protein</t>
+          <t>threonine synthase</t>
         </is>
       </c>
     </row>
@@ -11809,12 +11817,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Haladaptatus paucihalophilus</t>
+          <t>Halegenticoccus tardaugens</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>GCF_000376445.1</t>
+          <t>GCF_004116405.1</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -11830,46 +11838,46 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>NZ_AQXI01000001.1</t>
+          <t>NZ_SDIC01000004.1</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>23447</v>
+        <v>280663</v>
       </c>
       <c r="I42" t="n">
-        <v>23824</v>
+        <v>281940</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>NZ_AQXI01000001.1_29</t>
+          <t>NZ_SDIC01000004.1_296</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>125</v>
+        <v>425</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>OB_aCoA_assoc</t>
+          <t>FAD_binding_2 + NAD_binding_8 + Amino_oxidase</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>B208_RS0100150</t>
+          <t>C3L37_RS12360</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>WP_007978236.1</t>
+          <t>WP_129114918.1</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Zn-ribbon domain-containing OB-fold protein</t>
+          <t>NAD(P)/FAD-dependent oxidoreductase</t>
         </is>
       </c>
     </row>
@@ -11879,12 +11887,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Haladaptatus paucihalophilus</t>
+          <t>Halegenticoccus tardaugens</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>GCF_000376445.1</t>
+          <t>GCF_004116405.1</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -11900,61 +11908,61 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>NZ_AQXI01000001.1</t>
+          <t>NZ_SDIC01000004.1</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>22532</v>
+        <v>281948</v>
       </c>
       <c r="I43" t="n">
-        <v>23470</v>
+        <v>282988</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>NZ_AQXI01000001.1_28</t>
+          <t>NZ_SDIC01000004.1_297</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>312</v>
+        <v>346</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Abhydrolase_1 + Abhydrolase_6</t>
+          <t>ADH_N + ADH_zinc_N + ADH_zinc_N_2</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>B208_RS0100145</t>
+          <t>C3L37_RS12365</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>WP_007978234.1</t>
+          <t>WP_129114919.1</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>alpha/beta fold hydrolase</t>
+          <t>NAD(P)-dependent alcohol dehydrogenase</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Haladaptatus paucihalophilus</t>
+          <t>Haloprofundus marisrubri</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>GCF_000376445.1</t>
+          <t>GCF_001469955.1</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -11963,21 +11971,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6</v>
+        <v>-10</v>
       </c>
       <c r="F44" t="b">
         <v>0</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>NZ_AQXI01000001.1</t>
+          <t>NZ_LOPU01000018.1</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>21816</v>
+        <v>127683</v>
       </c>
       <c r="I44" t="n">
-        <v>22487</v>
+        <v>128351</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -11986,26 +11994,26 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>NZ_AQXI01000001.1_27</t>
+          <t>NZ_LOPU01000018.1_135</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>223</v>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>MeaB</t>
-        </is>
-      </c>
+        <v>222</v>
+      </c>
+      <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr">
         <is>
-          <t>B208_RS0100140</t>
-        </is>
-      </c>
-      <c r="O44" t="inlineStr"/>
+          <t>AUR64_RS06350</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>WP_155120539.1</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>methylmalonyl Co-A mutase-associated GTPase MeaB</t>
+          <t>hypothetical protein</t>
         </is>
       </c>
     </row>
@@ -12015,12 +12023,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Halorussus sp024138125</t>
+          <t>Haloprofundus marisrubri</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>GCF_024138125.1</t>
+          <t>GCF_001469955.1</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -12029,21 +12037,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="F45" t="b">
         <v>0</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>NZ_CP099993.1</t>
+          <t>NZ_LOPU01000018.1</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>935201</v>
+        <v>128387</v>
       </c>
       <c r="I45" t="n">
-        <v>935983</v>
+        <v>128671</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -12052,30 +12060,30 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>NZ_CP099993.1_949</t>
+          <t>NZ_LOPU01000018.1_136</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>260</v>
+        <v>94</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>HTH_24 + HTH_20 + MarR + MarR_2 + HTH_5 + HTH_27 + HTH_IclR</t>
+          <t>Ribosomal_L44</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>NGM10_RS04755</t>
+          <t>AUR64_RS06355</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>WP_253482358.1</t>
+          <t>WP_058581112.1</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>DUF7839 domain-containing protein</t>
+          <t>50S ribosomal protein L44e</t>
         </is>
       </c>
     </row>
@@ -12085,12 +12093,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Halorussus sp024138125</t>
+          <t>Haloprofundus marisrubri</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>GCF_024138125.1</t>
+          <t>GCF_001469955.1</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -12099,53 +12107,53 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="F46" t="b">
         <v>0</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>NZ_CP099993.1</t>
+          <t>NZ_LOPU01000018.1</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>935976</v>
+        <v>128676</v>
       </c>
       <c r="I46" t="n">
-        <v>936635</v>
+        <v>128849</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>NZ_CP099993.1_950</t>
+          <t>NZ_LOPU01000018.1_137</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>219</v>
+        <v>57</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>DnaJ</t>
+          <t>Ribosomal_S27e</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>NGM10_RS04760</t>
+          <t>AUR64_RS06360</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>WP_253483764.1</t>
+          <t>WP_058581113.1</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>J domain-containing protein</t>
+          <t>30S ribosomal protein S27e</t>
         </is>
       </c>
     </row>
@@ -12155,12 +12163,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Halorussus sp024138125</t>
+          <t>Haloprofundus marisrubri</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>GCF_024138125.1</t>
+          <t>GCF_001469955.1</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -12169,21 +12177,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="F47" t="b">
         <v>0</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>NZ_CP099993.1</t>
+          <t>NZ_LOPU01000018.1</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>936689</v>
+        <v>128865</v>
       </c>
       <c r="I47" t="n">
-        <v>937225</v>
+        <v>129665</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -12192,26 +12200,30 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>NZ_CP099993.1_951</t>
+          <t>NZ_LOPU01000018.1_138</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>178</v>
-      </c>
-      <c r="M47" t="inlineStr"/>
+        <v>266</v>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>S1 + EIF_2_alpha</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>NGM10_RS04765</t>
+          <t>AUR64_RS06365</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>WP_253482360.1</t>
+          <t>WP_058581114.1</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>DUF7344 domain-containing protein</t>
+          <t>translation initiation factor IF-2 subunit alpha</t>
         </is>
       </c>
     </row>
@@ -12221,12 +12233,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Halorussus sp024138125</t>
+          <t>Haloprofundus marisrubri</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>GCF_024138125.1</t>
+          <t>GCF_001469955.1</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -12235,53 +12247,53 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="F48" t="b">
         <v>0</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>NZ_CP099993.1</t>
+          <t>NZ_LOPU01000018.1</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>937258</v>
+        <v>129662</v>
       </c>
       <c r="I48" t="n">
-        <v>938016</v>
+        <v>129844</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>NZ_CP099993.1_952</t>
+          <t>NZ_LOPU01000018.1_139</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>252</v>
+        <v>60</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>PAC2</t>
+          <t>Nop10p</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>NGM10_RS04770</t>
+          <t>AUR64_RS20005</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>WP_253482362.1</t>
+          <t>WP_082230634.1</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>proteasome assembly chaperone family protein</t>
+          <t>RNA-protein complex protein Nop10</t>
         </is>
       </c>
     </row>
@@ -12291,12 +12303,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Halorussus sp024138125</t>
+          <t>Haloprofundus marisrubri</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>GCF_024138125.1</t>
+          <t>GCF_001469955.1</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -12305,53 +12317,53 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="F49" t="b">
         <v>0</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>NZ_CP099993.1</t>
+          <t>NZ_LOPU01000018.1</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>938022</v>
+        <v>129849</v>
       </c>
       <c r="I49" t="n">
-        <v>938204</v>
+        <v>130604</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>NZ_CP099993.1_953</t>
+          <t>NZ_LOPU01000018.1_140</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>60</v>
+        <v>251</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Nop10p</t>
+          <t>PAC2</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>NGM10_RS04775</t>
+          <t>AUR64_RS06370</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>WP_253482363.1</t>
+          <t>WP_058581115.1</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>RNA-protein complex protein Nop10</t>
+          <t>proteasome assembly chaperone family protein</t>
         </is>
       </c>
     </row>
@@ -12361,12 +12373,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Halorussus sp024138125</t>
+          <t>Haloprofundus marisrubri</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>GCF_024138125.1</t>
+          <t>GCF_001469955.1</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -12375,55 +12387,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="F50" t="b">
         <v>0</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>NZ_CP099993.1</t>
+          <t>NZ_LOPU01000018.1</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>938209</v>
+        <v>130743</v>
       </c>
       <c r="I50" t="n">
-        <v>939009</v>
+        <v>130874</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>NZ_CP099993.1_954</t>
+          <t>NZ_LOPU01000018.1_141</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>266</v>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>S1 + EIF_2_alpha</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>NGM10_RS04780</t>
-        </is>
-      </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>WP_253482364.1</t>
-        </is>
-      </c>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>translation initiation factor IF-2 subunit alpha</t>
-        </is>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -12431,12 +12427,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Halorussus sp024138125</t>
+          <t>Haloprofundus marisrubri</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>GCF_024138125.1</t>
+          <t>GCF_001469955.1</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -12445,21 +12441,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="F51" t="b">
         <v>0</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>NZ_CP099993.1</t>
+          <t>NZ_LOPU01000018.1</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>939006</v>
+        <v>130880</v>
       </c>
       <c r="I51" t="n">
-        <v>939179</v>
+        <v>131173</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -12468,30 +12464,26 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>NZ_CP099993.1_955</t>
+          <t>NZ_LOPU01000018.1_142</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>57</v>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>Ribosomal_S27e</t>
-        </is>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr">
         <is>
-          <t>NGM10_RS04785</t>
+          <t>AUR64_RS06375</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>WP_253482365.1</t>
+          <t>WP_058581116.1</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>30S ribosomal protein S27e</t>
+          <t>hypothetical protein</t>
         </is>
       </c>
     </row>
@@ -12501,12 +12493,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Halorussus sp024138125</t>
+          <t>Haloprofundus marisrubri</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>GCF_024138125.1</t>
+          <t>GCF_001469955.1</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -12515,21 +12507,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="F52" t="b">
         <v>0</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>NZ_CP099993.1</t>
+          <t>NZ_LOPU01000018.1</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>939184</v>
+        <v>131188</v>
       </c>
       <c r="I52" t="n">
-        <v>939459</v>
+        <v>131805</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -12538,30 +12530,30 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>NZ_CP099993.1_956</t>
+          <t>NZ_LOPU01000018.1_143</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>91</v>
+        <v>205</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Ribosomal_L44</t>
+          <t>DUF420</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>NGM10_RS04790</t>
+          <t>AUR64_RS06380</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>WP_128477830.1</t>
+          <t>WP_058581117.1</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>50S ribosomal protein L44e</t>
+          <t>DUF420 domain-containing protein</t>
         </is>
       </c>
     </row>
@@ -12571,12 +12563,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Halorussus sp024138125</t>
+          <t>Haloprofundus marisrubri</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>GCF_024138125.1</t>
+          <t>GCF_001469955.1</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -12585,43 +12577,53 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="F53" t="b">
         <v>0</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>NZ_CP099993.1</t>
+          <t>NZ_LOPU01000018.1</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>939791</v>
+        <v>131896</v>
       </c>
       <c r="I53" t="n">
-        <v>940027</v>
+        <v>132942</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>+</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>NZ_LOPU01000018.1_144</t>
+        </is>
+      </c>
+      <c r="L53" t="n">
+        <v>348</v>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>Fe-ADH + Fe-ADH_2 + DHQ_synthase</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>NGM10_RS04795</t>
+          <t>AUR64_RS06385</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>WP_253482366.1</t>
+          <t>WP_058581118.1</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>hypothetical protein</t>
+          <t>NAD(P)-dependent glycerol-1-phosphate dehydrogenase</t>
         </is>
       </c>
     </row>
@@ -12631,12 +12633,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Halorussus sp024138125</t>
+          <t>Haloprofundus marisrubri</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>GCF_024138125.1</t>
+          <t>GCF_001469955.1</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -12645,21 +12647,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="F54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>NZ_CP099993.1</t>
+          <t>NZ_LOPU01000018.1</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>940028</v>
+        <v>133145</v>
       </c>
       <c r="I54" t="n">
-        <v>940432</v>
+        <v>134038</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -12668,26 +12670,26 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>NZ_CP099993.1_957</t>
+          <t>NZ_LOPU01000018.1_145</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>134</v>
+        <v>297</v>
       </c>
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
-          <t>NGM10_RS04800</t>
+          <t>AUR64_RS06390</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>WP_253482367.1</t>
+          <t>WP_058581119.1</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>hypothetical protein</t>
+          <t>alpha/beta hydrolase</t>
         </is>
       </c>
     </row>
@@ -12697,12 +12699,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Halorussus sp024138125</t>
+          <t>Haloprofundus marisrubri</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>GCF_024138125.1</t>
+          <t>GCF_001469955.1</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -12711,53 +12713,53 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>NZ_CP099993.1</t>
+          <t>NZ_LOPU01000018.1</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>940489</v>
+        <v>134041</v>
       </c>
       <c r="I55" t="n">
-        <v>941391</v>
+        <v>134715</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>NZ_CP099993.1_958</t>
+          <t>NZ_LOPU01000018.1_146</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>300</v>
+        <v>224</v>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>DUF900</t>
+          <t>LysE</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>NGM10_RS04805</t>
+          <t>AUR64_RS06395</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>WP_253482368.1</t>
+          <t>WP_155120540.1</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>alpha/beta hydrolase</t>
+          <t>LysE family translocator</t>
         </is>
       </c>
     </row>
@@ -12767,12 +12769,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Halorussus sp024138125</t>
+          <t>Haloprofundus marisrubri</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>GCF_024138125.1</t>
+          <t>GCF_001469955.1</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -12781,49 +12783,53 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F56" t="b">
         <v>0</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>NZ_CP099993.1</t>
+          <t>NZ_LOPU01000018.1</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>941464</v>
+        <v>134845</v>
       </c>
       <c r="I56" t="n">
-        <v>941733</v>
+        <v>135537</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>NZ_CP099993.1_959</t>
+          <t>NZ_LOPU01000018.1_147</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>89</v>
-      </c>
-      <c r="M56" t="inlineStr"/>
+        <v>230</v>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>Fe_dep_repress + HTH_12 + MarR_2 + MarR + Fe_dep_repr_C + FeoA</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>NGM10_RS04810</t>
+          <t>AUR64_RS06400</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>WP_253482369.1</t>
+          <t>WP_058581120.1</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>HAH_0734 family protein</t>
+          <t>metal-dependent transcriptional regulator</t>
         </is>
       </c>
     </row>
@@ -12833,12 +12839,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Halorussus sp024138125</t>
+          <t>Haloprofundus marisrubri</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>GCF_024138125.1</t>
+          <t>GCF_001469955.1</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -12847,21 +12853,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F57" t="b">
         <v>0</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>NZ_CP099993.1</t>
+          <t>NZ_LOPU01000018.1</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>941756</v>
+        <v>135590</v>
       </c>
       <c r="I57" t="n">
-        <v>941971</v>
+        <v>136912</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -12870,26 +12876,30 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>NZ_CP099993.1_960</t>
+          <t>NZ_LOPU01000018.1_148</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>71</v>
-      </c>
-      <c r="M57" t="inlineStr"/>
+        <v>440</v>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>FAD_binding_3 + NAD_binding_8</t>
+        </is>
+      </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>NGM10_RS18345</t>
+          <t>AUR64_RS06405</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>WP_253482371.1</t>
+          <t>WP_058581831.1</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>hypothetical protein</t>
+          <t>FAD-dependent oxidoreductase</t>
         </is>
       </c>
     </row>
@@ -12899,12 +12909,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Halorussus sp024138125</t>
+          <t>Haloprofundus marisrubri</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>GCF_024138125.1</t>
+          <t>GCF_001469955.1</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -12913,21 +12923,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F58" t="b">
         <v>0</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>NZ_CP099993.1</t>
+          <t>NZ_LOPU01000018.1</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>942022</v>
+        <v>137043</v>
       </c>
       <c r="I58" t="n">
-        <v>943314</v>
+        <v>138236</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -12936,30 +12946,30 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>NZ_CP099993.1_961</t>
+          <t>NZ_LOPU01000018.1_149</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>430</v>
+        <v>397</v>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>MFS_1</t>
+          <t>PALP</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>NGM10_RS04820</t>
+          <t>AUR64_RS06410</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>WP_368408655.1</t>
+          <t>WP_058581121.1</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>MFS transporter</t>
+          <t>threonine synthase</t>
         </is>
       </c>
     </row>
@@ -12969,12 +12979,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Halorussus sp024138125</t>
+          <t>Haloprofundus marisrubri</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>GCF_024138125.1</t>
+          <t>GCF_001469955.1</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -12983,64 +12993,68 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F59" t="b">
         <v>0</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>NZ_CP099993.1</t>
+          <t>NZ_LOPU01000018.1</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>943440</v>
+        <v>138369</v>
       </c>
       <c r="I59" t="n">
-        <v>943835</v>
+        <v>139655</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>NZ_CP099993.1_962</t>
+          <t>NZ_LOPU01000018.1_150</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>131</v>
-      </c>
-      <c r="M59" t="inlineStr"/>
+        <v>428</v>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>FAD_binding_3 + FAD_binding_2 + NAD_binding_8 + Amino_oxidase</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>NGM10_RS04825</t>
+          <t>AUR64_RS06415</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>WP_253482374.1</t>
+          <t>WP_058581122.1</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>hypothetical protein</t>
+          <t>NAD(P)/FAD-dependent oxidoreductase</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Halorussus sp024138125</t>
+          <t>Halococcus sediminicola</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>GCF_024138125.1</t>
+          <t>GCF_000755245.1</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -13049,21 +13063,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5</v>
+        <v>-6</v>
       </c>
       <c r="F60" t="b">
         <v>0</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>NZ_CP099993.1</t>
+          <t>NZ_BBMP01000023.1</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>944171</v>
+        <v>98609</v>
       </c>
       <c r="I60" t="n">
-        <v>944677</v>
+        <v>99829</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -13072,45 +13086,45 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>NZ_CP099993.1_963</t>
+          <t>NZ_BBMP01000023.1_101</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>168</v>
+        <v>406</v>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>CinA</t>
+          <t>Orn_DAP_Arg_deC + Ala_racemase_N + Orn_Arg_deC_N</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>NGM10_RS04830</t>
+          <t>ACP97_RS14740</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>WP_253482376.1</t>
+          <t>WP_049998598.1</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>CinA family protein</t>
+          <t>diaminopimelate decarboxylase</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Halorussus sp024138125</t>
+          <t>Halococcus sediminicola</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>GCF_024138125.1</t>
+          <t>GCF_000755245.1</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -13119,21 +13133,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6</v>
+        <v>-5</v>
       </c>
       <c r="F61" t="b">
         <v>0</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>NZ_CP099993.1</t>
+          <t>NZ_BBMP01000023.1</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>944755</v>
+        <v>98469</v>
       </c>
       <c r="I61" t="n">
-        <v>945243</v>
+        <v>98612</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -13142,45 +13156,29 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>NZ_CP099993.1_964</t>
+          <t>NZ_BBMP01000023.1_100</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>162</v>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>YdjM</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>NGM10_RS04835</t>
-        </is>
-      </c>
-      <c r="O61" t="inlineStr">
-        <is>
-          <t>WP_253482379.1</t>
-        </is>
-      </c>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t>metal-dependent hydrolase</t>
-        </is>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Halorussus sp024138125</t>
+          <t>Halococcus sediminicola</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>GCF_024138125.1</t>
+          <t>GCF_000755245.1</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -13189,21 +13187,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>7</v>
+        <v>-4</v>
       </c>
       <c r="F62" t="b">
         <v>0</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>NZ_CP099993.1</t>
+          <t>NZ_BBMP01000023.1</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>945240</v>
+        <v>97419</v>
       </c>
       <c r="I62" t="n">
-        <v>945995</v>
+        <v>98264</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -13212,45 +13210,45 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>NZ_CP099993.1_965</t>
+          <t>NZ_BBMP01000023.1_99</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>251</v>
+        <v>281</v>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>PHP_C</t>
+          <t>Peptidase_M55</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>NGM10_RS04840</t>
+          <t>ACP97_RS14735</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>WP_253482381.1</t>
+          <t>WP_049998597.1</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>PHP domain-containing protein</t>
+          <t>M55 family metallopeptidase</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Halorussus sp024138125</t>
+          <t>Halococcus sediminicola</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>GCF_024138125.1</t>
+          <t>GCF_000755245.1</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -13259,53 +13257,53 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>8</v>
+        <v>-3</v>
       </c>
       <c r="F63" t="b">
         <v>0</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>NZ_CP099993.1</t>
+          <t>NZ_BBMP01000023.1</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>946138</v>
+        <v>96076</v>
       </c>
       <c r="I63" t="n">
-        <v>946782</v>
+        <v>96885</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>NZ_CP099993.1_966</t>
+          <t>NZ_BBMP01000023.1_98</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>214</v>
+        <v>269</v>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Hydrolase + HAD + HAD_2 + Hydrolase_like</t>
+          <t>Glucosaminidase</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>NGM10_RS04845</t>
+          <t>ACP97_RS14730</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>WP_253482383.1</t>
+          <t>WP_049998596.1</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>HAD family hydrolase</t>
+          <t>glucosaminidase domain-containing protein</t>
         </is>
       </c>
     </row>
@@ -13315,12 +13313,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Halegenticoccus tardaugens</t>
+          <t>Halococcus sediminicola</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>GCF_004116405.1</t>
+          <t>GCF_000755245.1</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -13329,49 +13327,53 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>-9</v>
+        <v>-2</v>
       </c>
       <c r="F64" t="b">
         <v>0</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>NZ_SDIC01000004.1</t>
+          <t>NZ_BBMP01000023.1</t>
         </is>
       </c>
       <c r="H64" t="n">
-        <v>271224</v>
+        <v>95284</v>
       </c>
       <c r="I64" t="n">
-        <v>271868</v>
+        <v>96036</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>NZ_SDIC01000004.1_283</t>
+          <t>NZ_BBMP01000023.1_97</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>214</v>
-      </c>
-      <c r="M64" t="inlineStr"/>
+        <v>250</v>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>Peptidase_M23</t>
+        </is>
+      </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>C3L37_RS12300</t>
+          <t>ACP97_RS19190</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>WP_129114908.1</t>
+          <t>WP_154020021.1</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>hypothetical protein</t>
+          <t>M23 family metallopeptidase</t>
         </is>
       </c>
     </row>
@@ -13381,12 +13383,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Halegenticoccus tardaugens</t>
+          <t>Halococcus sediminicola</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>GCF_004116405.1</t>
+          <t>GCF_000755245.1</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13395,53 +13397,53 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>-8</v>
+        <v>-1</v>
       </c>
       <c r="F65" t="b">
         <v>0</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>NZ_SDIC01000004.1</t>
+          <t>NZ_BBMP01000023.1</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>271904</v>
+        <v>94405</v>
       </c>
       <c r="I65" t="n">
-        <v>272188</v>
+        <v>95268</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>NZ_SDIC01000004.1_284</t>
+          <t>NZ_BBMP01000023.1_96</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>94</v>
+        <v>287</v>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Ribosomal_L44</t>
+          <t>Amidase_2</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>C3L37_RS12305</t>
+          <t>ACP97_RS19185</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>WP_129114909.1</t>
+          <t>WP_079977648.1</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>50S ribosomal protein L44e</t>
+          <t>N-acetylmuramoyl-L-alanine amidase</t>
         </is>
       </c>
     </row>
@@ -13451,12 +13453,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Halegenticoccus tardaugens</t>
+          <t>Halococcus sediminicola</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>GCF_004116405.1</t>
+          <t>GCF_000755245.1</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13465,53 +13467,53 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
       <c r="F66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>NZ_SDIC01000004.1</t>
+          <t>NZ_BBMP01000023.1</t>
         </is>
       </c>
       <c r="H66" t="n">
-        <v>272193</v>
+        <v>93325</v>
       </c>
       <c r="I66" t="n">
-        <v>272366</v>
+        <v>94206</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>NZ_SDIC01000004.1_285</t>
+          <t>NZ_BBMP01000023.1_95</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>57</v>
+        <v>293</v>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Ribosomal_S27e</t>
+          <t>DUF900</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>C3L37_RS12310</t>
+          <t>ACP97_RS14715</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>WP_129114910.1</t>
+          <t>WP_394297709.1</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>30S ribosomal protein S27e</t>
+          <t>alpha/beta hydrolase</t>
         </is>
       </c>
     </row>
@@ -13521,12 +13523,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Halegenticoccus tardaugens</t>
+          <t>Halococcus sediminicola</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>GCF_004116405.1</t>
+          <t>GCF_000755245.1</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13535,21 +13537,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>-6</v>
+        <v>1</v>
       </c>
       <c r="F67" t="b">
         <v>0</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>NZ_SDIC01000004.1</t>
+          <t>NZ_BBMP01000023.1</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>272382</v>
+        <v>92436</v>
       </c>
       <c r="I67" t="n">
-        <v>273182</v>
+        <v>93197</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -13558,30 +13560,26 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>NZ_SDIC01000004.1_286</t>
+          <t>NZ_BBMP01000023.1_94</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>266</v>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>S1 + EIF_2_alpha</t>
-        </is>
-      </c>
+        <v>253</v>
+      </c>
+      <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr">
         <is>
-          <t>C3L37_RS12315</t>
+          <t>ACP97_RS14710</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>WP_129114911.1</t>
+          <t>WP_237561187.1</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>translation initiation factor IF-2 subunit alpha</t>
+          <t>hypothetical protein</t>
         </is>
       </c>
     </row>
@@ -13591,12 +13589,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Halegenticoccus tardaugens</t>
+          <t>Halococcus sediminicola</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>GCF_004116405.1</t>
+          <t>GCF_000755245.1</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13605,21 +13603,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>-5</v>
+        <v>2</v>
       </c>
       <c r="F68" t="b">
         <v>0</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>NZ_SDIC01000004.1</t>
+          <t>NZ_BBMP01000023.1</t>
         </is>
       </c>
       <c r="H68" t="n">
-        <v>273187</v>
+        <v>92083</v>
       </c>
       <c r="I68" t="n">
-        <v>273372</v>
+        <v>92256</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
@@ -13628,32 +13626,16 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>NZ_SDIC01000004.1_287</t>
+          <t>NZ_BBMP01000023.1_93</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>61</v>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>Nop10p</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>C3L37_RS12320</t>
-        </is>
-      </c>
-      <c r="O68" t="inlineStr">
-        <is>
-          <t>WP_129114912.1</t>
-        </is>
-      </c>
-      <c r="P68" t="inlineStr">
-        <is>
-          <t>RNA-protein complex protein Nop10</t>
-        </is>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -13661,12 +13643,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Halegenticoccus tardaugens</t>
+          <t>Halococcus sediminicola</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>GCF_004116405.1</t>
+          <t>GCF_000755245.1</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13675,21 +13657,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>-4</v>
+        <v>3</v>
       </c>
       <c r="F69" t="b">
         <v>0</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>NZ_SDIC01000004.1</t>
+          <t>NZ_BBMP01000023.1</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>273460</v>
+        <v>91669</v>
       </c>
       <c r="I69" t="n">
-        <v>274215</v>
+        <v>91944</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
@@ -13698,32 +13680,16 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>NZ_SDIC01000004.1_288</t>
+          <t>NZ_BBMP01000023.1_92</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>251</v>
-      </c>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>PAC2</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t>C3L37_RS12325</t>
-        </is>
-      </c>
-      <c r="O69" t="inlineStr">
-        <is>
-          <t>WP_129114913.1</t>
-        </is>
-      </c>
-      <c r="P69" t="inlineStr">
-        <is>
-          <t>proteasome assembly chaperone family protein</t>
-        </is>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -13731,12 +13697,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Halegenticoccus tardaugens</t>
+          <t>Halococcus sediminicola</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>GCF_004116405.1</t>
+          <t>GCF_000755245.1</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -13745,49 +13711,53 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>-3</v>
+        <v>4</v>
       </c>
       <c r="F70" t="b">
         <v>0</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>NZ_SDIC01000004.1</t>
+          <t>NZ_BBMP01000023.1</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>274326</v>
+        <v>90005</v>
       </c>
       <c r="I70" t="n">
-        <v>274496</v>
+        <v>91369</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>NZ_SDIC01000004.1_289</t>
+          <t>NZ_BBMP01000023.1_91</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>56</v>
-      </c>
-      <c r="M70" t="inlineStr"/>
+        <v>454</v>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>Sulfatase</t>
+        </is>
+      </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>C3L37_RS24370</t>
+          <t>ACP97_RS14705</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>WP_164974745.1</t>
+          <t>WP_049998594.1</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>hypothetical protein</t>
+          <t>sulfatase-like hydrolase/transferase</t>
         </is>
       </c>
     </row>
@@ -13797,12 +13767,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Halegenticoccus tardaugens</t>
+          <t>Halococcus sediminicola</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>GCF_004116405.1</t>
+          <t>GCF_000755245.1</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -13811,53 +13781,49 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>-2</v>
+        <v>5</v>
       </c>
       <c r="F71" t="b">
         <v>0</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>NZ_SDIC01000004.1</t>
+          <t>NZ_BBMP01000023.1</t>
         </is>
       </c>
       <c r="H71" t="n">
-        <v>274595</v>
+        <v>89058</v>
       </c>
       <c r="I71" t="n">
-        <v>275212</v>
+        <v>90008</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>NZ_SDIC01000004.1_290</t>
+          <t>NZ_BBMP01000023.1_90</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>205</v>
-      </c>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>DUF420</t>
-        </is>
-      </c>
+        <v>316</v>
+      </c>
+      <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr">
         <is>
-          <t>C3L37_RS12330</t>
+          <t>ACP97_RS14700</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>WP_129114914.1</t>
+          <t>WP_049998593.1</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>DUF420 domain-containing protein</t>
+          <t>alkaline phosphatase family protein</t>
         </is>
       </c>
     </row>
@@ -13867,12 +13833,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Halegenticoccus tardaugens</t>
+          <t>Halococcus sediminicola</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>GCF_004116405.1</t>
+          <t>GCF_000755245.1</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -13881,21 +13847,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F72" t="b">
         <v>0</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>NZ_SDIC01000004.1</t>
+          <t>NZ_BBMP01000023.1</t>
         </is>
       </c>
       <c r="H72" t="n">
-        <v>275382</v>
+        <v>88276</v>
       </c>
       <c r="I72" t="n">
-        <v>276434</v>
+        <v>88380</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
@@ -13904,45 +13870,29 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>NZ_SDIC01000004.1_291</t>
+          <t>NZ_BBMP01000023.1_89</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>350</v>
-      </c>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>Fe-ADH + Fe-ADH_2 + DHQ_synthase</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr">
-        <is>
-          <t>C3L37_RS12335</t>
-        </is>
-      </c>
-      <c r="O72" t="inlineStr">
-        <is>
-          <t>WP_129114915.1</t>
-        </is>
-      </c>
-      <c r="P72" t="inlineStr">
-        <is>
-          <t>NAD(P)-dependent glycerol-1-phosphate dehydrogenase</t>
-        </is>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Halegenticoccus tardaugens</t>
+          <t>Halocatena sp023276375</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>GCF_004116405.1</t>
+          <t>GCF_023276375.1</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -13951,68 +13901,68 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="F73" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>NZ_SDIC01000004.1</t>
+          <t>NZ_JALLPK010000001.1</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>276759</v>
+        <v>2725703</v>
       </c>
       <c r="I73" t="n">
-        <v>277637</v>
+        <v>2726368</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>NZ_SDIC01000004.1_292</t>
+          <t>NZ_JALLPK010000001.1_2680</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>292</v>
+        <v>221</v>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>DUF900</t>
+          <t>LysE</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>C3L37_RS12340</t>
+          <t>MW898_RS12610</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>WP_129115263.1</t>
+          <t>WP_368409092.1</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>alpha/beta hydrolase</t>
+          <t>LysE family translocator</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Halegenticoccus tardaugens</t>
+          <t>Halocatena sp023276375</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>GCF_004116405.1</t>
+          <t>GCF_023276375.1</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14021,21 +13971,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1</v>
+        <v>-7</v>
       </c>
       <c r="F74" t="b">
         <v>0</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>NZ_SDIC01000004.1</t>
+          <t>NZ_JALLPK010000001.1</t>
         </is>
       </c>
       <c r="H74" t="n">
-        <v>277692</v>
+        <v>2726495</v>
       </c>
       <c r="I74" t="n">
-        <v>278429</v>
+        <v>2727667</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
@@ -14044,45 +13994,45 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>NZ_SDIC01000004.1_293</t>
+          <t>NZ_JALLPK010000001.1_2681</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>245</v>
+        <v>390</v>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>LysE</t>
+          <t>PALP</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>C3L37_RS12345</t>
+          <t>MW898_RS12615</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>WP_129115264.1</t>
+          <t>WP_248907824.1</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>LysE family translocator</t>
+          <t>threonine synthase</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Halegenticoccus tardaugens</t>
+          <t>Halocatena sp023276375</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>GCF_004116405.1</t>
+          <t>GCF_023276375.1</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -14091,21 +14041,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2</v>
+        <v>-6</v>
       </c>
       <c r="F75" t="b">
         <v>0</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>NZ_SDIC01000004.1</t>
+          <t>NZ_JALLPK010000001.1</t>
         </is>
       </c>
       <c r="H75" t="n">
-        <v>278512</v>
+        <v>2727863</v>
       </c>
       <c r="I75" t="n">
-        <v>279186</v>
+        <v>2728456</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
@@ -14114,45 +14064,45 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>NZ_SDIC01000004.1_294</t>
+          <t>NZ_JALLPK010000001.1_2682</t>
         </is>
       </c>
       <c r="L75" t="n">
-        <v>224</v>
+        <v>197</v>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Fe_dep_repress + MarR_2 + MarR + HTH_IclR + Fe_dep_repr_C + FeoA</t>
+          <t>DnaJ</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>C3L37_RS12350</t>
+          <t>MW898_RS12620</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>WP_129114916.1</t>
+          <t>WP_248907826.1</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>metal-dependent transcriptional regulator</t>
+          <t>J domain-containing protein</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Halegenticoccus tardaugens</t>
+          <t>Halocatena sp023276375</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>GCF_004116405.1</t>
+          <t>GCF_023276375.1</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -14161,21 +14111,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>3</v>
+        <v>-5</v>
       </c>
       <c r="F76" t="b">
         <v>0</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>NZ_SDIC01000004.1</t>
+          <t>NZ_JALLPK010000001.1</t>
         </is>
       </c>
       <c r="H76" t="n">
-        <v>279308</v>
+        <v>2728598</v>
       </c>
       <c r="I76" t="n">
-        <v>280501</v>
+        <v>2729386</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
@@ -14184,45 +14134,45 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>NZ_SDIC01000004.1_295</t>
+          <t>NZ_JALLPK010000001.1_2683</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>397</v>
+        <v>262</v>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>PALP</t>
+          <t>PAC2</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>C3L37_RS12355</t>
+          <t>MW898_RS12625</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>WP_129114917.1</t>
+          <t>WP_248907828.1</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>threonine synthase</t>
+          <t>proteasome assembly chaperone family protein</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Halegenticoccus tardaugens</t>
+          <t>Halocatena sp023276375</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>GCF_004116405.1</t>
+          <t>GCF_023276375.1</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -14231,68 +14181,68 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4</v>
+        <v>-4</v>
       </c>
       <c r="F77" t="b">
         <v>0</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>NZ_SDIC01000004.1</t>
+          <t>NZ_JALLPK010000001.1</t>
         </is>
       </c>
       <c r="H77" t="n">
-        <v>280663</v>
+        <v>2729392</v>
       </c>
       <c r="I77" t="n">
-        <v>281940</v>
+        <v>2729574</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>NZ_SDIC01000004.1_296</t>
+          <t>NZ_JALLPK010000001.1_2684</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>425</v>
+        <v>60</v>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>FAD_binding_2 + NAD_binding_8 + Amino_oxidase</t>
+          <t>Nop10p</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>C3L37_RS12360</t>
+          <t>MW898_RS12630</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>WP_129114918.1</t>
+          <t>WP_248907837.1</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>NAD(P)/FAD-dependent oxidoreductase</t>
+          <t>RNA-protein complex protein Nop10</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Halegenticoccus tardaugens</t>
+          <t>Halocatena sp023276375</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>GCF_004116405.1</t>
+          <t>GCF_023276375.1</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -14301,21 +14251,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5</v>
+        <v>-3</v>
       </c>
       <c r="F78" t="b">
         <v>0</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>NZ_SDIC01000004.1</t>
+          <t>NZ_JALLPK010000001.1</t>
         </is>
       </c>
       <c r="H78" t="n">
-        <v>281948</v>
+        <v>2729606</v>
       </c>
       <c r="I78" t="n">
-        <v>282988</v>
+        <v>2730406</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
@@ -14324,30 +14274,30 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>NZ_SDIC01000004.1_297</t>
+          <t>NZ_JALLPK010000001.1_2685</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>346</v>
+        <v>266</v>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>ADH_N + ADH_zinc_N + ADH_zinc_N_2</t>
+          <t>S1 + EIF_2_alpha</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>C3L37_RS12365</t>
+          <t>MW898_RS12635</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>WP_129114919.1</t>
+          <t>WP_248907839.1</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>NAD(P)-dependent alcohol dehydrogenase</t>
+          <t>translation initiation factor IF-2 subunit alpha</t>
         </is>
       </c>
     </row>
@@ -14357,12 +14307,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Halococcus sediminicola</t>
+          <t>Halocatena sp023276375</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>GCF_000755245.1</t>
+          <t>GCF_023276375.1</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -14371,53 +14321,53 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>-6</v>
+        <v>-2</v>
       </c>
       <c r="F79" t="b">
         <v>0</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>NZ_BBMP01000023.1</t>
+          <t>NZ_JALLPK010000001.1</t>
         </is>
       </c>
       <c r="H79" t="n">
-        <v>98609</v>
+        <v>2730568</v>
       </c>
       <c r="I79" t="n">
-        <v>99829</v>
+        <v>2730753</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>NZ_BBMP01000023.1_101</t>
+          <t>NZ_JALLPK010000001.1_2686</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>406</v>
+        <v>61</v>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Orn_DAP_Arg_deC + Ala_racemase_N + Orn_Arg_deC_N</t>
+          <t>Ribosomal_S27e</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>ACP97_RS14740</t>
+          <t>MW898_RS12640</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>WP_049998598.1</t>
+          <t>WP_248907841.1</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>diaminopimelate decarboxylase</t>
+          <t>30S ribosomal protein S27e</t>
         </is>
       </c>
     </row>
@@ -14427,12 +14377,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Halococcus sediminicola</t>
+          <t>Halocatena sp023276375</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>GCF_000755245.1</t>
+          <t>GCF_023276375.1</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -14441,39 +14391,55 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="F80" t="b">
         <v>0</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>NZ_BBMP01000023.1</t>
+          <t>NZ_JALLPK010000001.1</t>
         </is>
       </c>
       <c r="H80" t="n">
-        <v>98469</v>
+        <v>2730756</v>
       </c>
       <c r="I80" t="n">
-        <v>98612</v>
+        <v>2731040</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>NZ_BBMP01000023.1_100</t>
+          <t>NZ_JALLPK010000001.1_2687</t>
         </is>
       </c>
       <c r="L80" t="n">
-        <v>47</v>
-      </c>
-      <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
-      <c r="O80" t="inlineStr"/>
-      <c r="P80" t="inlineStr"/>
+        <v>94</v>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>Ribosomal_L44</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>MW898_RS12645</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>WP_248907843.1</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>50S ribosomal protein L44e</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -14481,12 +14447,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Halococcus sediminicola</t>
+          <t>Halocatena sp023276375</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>GCF_000755245.1</t>
+          <t>GCF_023276375.1</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -14495,53 +14461,49 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="F81" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>NZ_BBMP01000023.1</t>
+          <t>NZ_JALLPK010000001.1</t>
         </is>
       </c>
       <c r="H81" t="n">
-        <v>97419</v>
+        <v>2731297</v>
       </c>
       <c r="I81" t="n">
-        <v>98264</v>
+        <v>2732199</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>NZ_BBMP01000023.1_99</t>
+          <t>NZ_JALLPK010000001.1_2688</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>281</v>
-      </c>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>Peptidase_M55</t>
-        </is>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr">
         <is>
-          <t>ACP97_RS14735</t>
+          <t>MW898_RS12650</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>WP_049998597.1</t>
+          <t>WP_248907845.1</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>M55 family metallopeptidase</t>
+          <t>hypothetical protein</t>
         </is>
       </c>
     </row>
@@ -14551,12 +14513,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Halococcus sediminicola</t>
+          <t>Halocatena sp023276375</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>GCF_000755245.1</t>
+          <t>GCF_023276375.1</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -14565,21 +14527,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>-3</v>
+        <v>1</v>
       </c>
       <c r="F82" t="b">
         <v>0</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>NZ_BBMP01000023.1</t>
+          <t>NZ_JALLPK010000001.1</t>
         </is>
       </c>
       <c r="H82" t="n">
-        <v>96076</v>
+        <v>2732202</v>
       </c>
       <c r="I82" t="n">
-        <v>96885</v>
+        <v>2733191</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
@@ -14588,30 +14550,30 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>NZ_BBMP01000023.1_98</t>
+          <t>NZ_JALLPK010000001.1_2689</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>269</v>
+        <v>329</v>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Glucosaminidase</t>
+          <t>OCD_Mu_crystall</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>ACP97_RS14730</t>
+          <t>MW898_RS12655</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>WP_049998596.1</t>
+          <t>WP_248907846.1</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>glucosaminidase domain-containing protein</t>
+          <t>ornithine cyclodeaminase family protein</t>
         </is>
       </c>
     </row>
@@ -14621,12 +14583,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Halococcus sediminicola</t>
+          <t>Halocatena sp023276375</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>GCF_000755245.1</t>
+          <t>GCF_023276375.1</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -14635,21 +14597,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="F83" t="b">
         <v>0</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>NZ_BBMP01000023.1</t>
+          <t>NZ_JALLPK010000001.1</t>
         </is>
       </c>
       <c r="H83" t="n">
-        <v>95284</v>
+        <v>2733246</v>
       </c>
       <c r="I83" t="n">
-        <v>96036</v>
+        <v>2733473</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
@@ -14658,30 +14620,26 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>NZ_BBMP01000023.1_97</t>
+          <t>NZ_JALLPK010000001.1_2690</t>
         </is>
       </c>
       <c r="L83" t="n">
-        <v>250</v>
-      </c>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>Peptidase_M23</t>
-        </is>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="M83" t="inlineStr"/>
       <c r="N83" t="inlineStr">
         <is>
-          <t>ACP97_RS19190</t>
+          <t>MW898_RS12660</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>WP_154020021.1</t>
+          <t>WP_248907848.1</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>M23 family metallopeptidase</t>
+          <t>DUF8015 family protein</t>
         </is>
       </c>
     </row>
@@ -14691,12 +14649,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Halococcus sediminicola</t>
+          <t>Halocatena sp023276375</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>GCF_000755245.1</t>
+          <t>GCF_023276375.1</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -14705,53 +14663,53 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="F84" t="b">
         <v>0</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>NZ_BBMP01000023.1</t>
+          <t>NZ_JALLPK010000001.1</t>
         </is>
       </c>
       <c r="H84" t="n">
-        <v>94405</v>
+        <v>2734018</v>
       </c>
       <c r="I84" t="n">
-        <v>95268</v>
+        <v>2735277</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>NZ_BBMP01000023.1_96</t>
+          <t>NZ_JALLPK010000001.1_2691</t>
         </is>
       </c>
       <c r="L84" t="n">
-        <v>287</v>
+        <v>419</v>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Amidase_2</t>
+          <t>MFS_1</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>ACP97_RS19185</t>
+          <t>MW898_RS12665</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>WP_079977648.1</t>
+          <t>WP_248907850.1</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>N-acetylmuramoyl-L-alanine amidase</t>
+          <t>MFS transporter</t>
         </is>
       </c>
     </row>
@@ -14761,12 +14719,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Halococcus sediminicola</t>
+          <t>Halocatena sp023276375</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>GCF_000755245.1</t>
+          <t>GCF_023276375.1</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -14775,21 +14733,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F85" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>NZ_BBMP01000023.1</t>
+          <t>NZ_JALLPK010000001.1</t>
         </is>
       </c>
       <c r="H85" t="n">
-        <v>93325</v>
+        <v>2735298</v>
       </c>
       <c r="I85" t="n">
-        <v>94206</v>
+        <v>2735843</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
@@ -14798,30 +14756,30 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>NZ_BBMP01000023.1_95</t>
+          <t>NZ_JALLPK010000001.1_2692</t>
         </is>
       </c>
       <c r="L85" t="n">
-        <v>293</v>
+        <v>181</v>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>DUF900</t>
+          <t>DUF3054</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>ACP97_RS14715</t>
+          <t>MW898_RS12670</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>WP_394297709.1</t>
+          <t>WP_248907851.1</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>alpha/beta hydrolase</t>
+          <t>DUF3054 domain-containing protein</t>
         </is>
       </c>
     </row>
@@ -14831,12 +14789,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Halococcus sediminicola</t>
+          <t>Halocatena sp023276375</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>GCF_000755245.1</t>
+          <t>GCF_023276375.1</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -14845,21 +14803,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F86" t="b">
         <v>0</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>NZ_BBMP01000023.1</t>
+          <t>NZ_JALLPK010000001.1</t>
         </is>
       </c>
       <c r="H86" t="n">
-        <v>92436</v>
+        <v>2735849</v>
       </c>
       <c r="I86" t="n">
-        <v>93197</v>
+        <v>2736379</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
@@ -14868,26 +14826,30 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>NZ_BBMP01000023.1_94</t>
+          <t>NZ_JALLPK010000001.1_2693</t>
         </is>
       </c>
       <c r="L86" t="n">
-        <v>253</v>
-      </c>
-      <c r="M86" t="inlineStr"/>
+        <v>176</v>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>Acetyltransf_1</t>
+        </is>
+      </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>ACP97_RS14710</t>
+          <t>MW898_RS12675</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>WP_237561187.1</t>
+          <t>WP_248907853.1</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>hypothetical protein</t>
+          <t>GNAT family N-acetyltransferase</t>
         </is>
       </c>
     </row>
@@ -14897,12 +14859,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Halococcus sediminicola</t>
+          <t>Halocatena sp023276375</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>GCF_000755245.1</t>
+          <t>GCF_023276375.1</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -14911,21 +14873,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F87" t="b">
         <v>0</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>NZ_BBMP01000023.1</t>
+          <t>NZ_JALLPK010000001.1</t>
         </is>
       </c>
       <c r="H87" t="n">
-        <v>92083</v>
+        <v>2736406</v>
       </c>
       <c r="I87" t="n">
-        <v>92256</v>
+        <v>2737380</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
@@ -14934,29 +14896,45 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>NZ_BBMP01000023.1_93</t>
+          <t>NZ_JALLPK010000001.1_2694</t>
         </is>
       </c>
       <c r="L87" t="n">
-        <v>57</v>
-      </c>
-      <c r="M87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
-      <c r="O87" t="inlineStr"/>
-      <c r="P87" t="inlineStr"/>
+        <v>324</v>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>XPG_N + XPG_I</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>MW898_RS12680</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>WP_248907855.1</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>flap endonuclease-1</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Halococcus sediminicola</t>
+          <t>Halomarina oriensis</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>GCF_000755245.1</t>
+          <t>GCF_009791395.1</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -14965,52 +14943,64 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>3</v>
+        <v>-8</v>
       </c>
       <c r="F88" t="b">
         <v>0</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>NZ_BBMP01000023.1</t>
+          <t>NZ_WSZK01000006.1</t>
         </is>
       </c>
       <c r="H88" t="n">
-        <v>91669</v>
+        <v>104745</v>
       </c>
       <c r="I88" t="n">
-        <v>91944</v>
+        <v>105908</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>NZ_BBMP01000023.1_92</t>
+          <t>NZ_WSZK01000006.1_124</t>
         </is>
       </c>
       <c r="L88" t="n">
-        <v>91</v>
+        <v>387</v>
       </c>
       <c r="M88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
-      <c r="O88" t="inlineStr"/>
-      <c r="P88" t="inlineStr"/>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>GQS65_RS02380</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>WP_158203068.1</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>hypothetical protein</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Halococcus sediminicola</t>
+          <t>Halomarina oriensis</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>GCF_000755245.1</t>
+          <t>GCF_009791395.1</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -15019,21 +15009,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4</v>
+        <v>-7</v>
       </c>
       <c r="F89" t="b">
         <v>0</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>NZ_BBMP01000023.1</t>
+          <t>NZ_WSZK01000006.1</t>
         </is>
       </c>
       <c r="H89" t="n">
-        <v>90005</v>
+        <v>103404</v>
       </c>
       <c r="I89" t="n">
-        <v>91369</v>
+        <v>104561</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
@@ -15042,45 +15032,45 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>NZ_BBMP01000023.1_91</t>
+          <t>NZ_WSZK01000006.1_123</t>
         </is>
       </c>
       <c r="L89" t="n">
-        <v>454</v>
+        <v>385</v>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Sulfatase</t>
+          <t>Acyl-CoA_dh_N + Acyl-CoA_dh_M + Acyl-CoA_dh_1 + Acyl-CoA_dh_2</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>ACP97_RS14705</t>
+          <t>GQS65_RS02375</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>WP_049998594.1</t>
+          <t>WP_158203067.1</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>sulfatase-like hydrolase/transferase</t>
+          <t>acyl-CoA dehydrogenase family protein</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Halococcus sediminicola</t>
+          <t>Halomarina oriensis</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>GCF_000755245.1</t>
+          <t>GCF_009791395.1</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -15089,64 +15079,52 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>5</v>
+        <v>-6</v>
       </c>
       <c r="F90" t="b">
         <v>0</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>NZ_BBMP01000023.1</t>
+          <t>NZ_WSZK01000006.1</t>
         </is>
       </c>
       <c r="H90" t="n">
-        <v>89058</v>
+        <v>103204</v>
       </c>
       <c r="I90" t="n">
-        <v>90008</v>
+        <v>103323</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>NZ_BBMP01000023.1_90</t>
+          <t>NZ_WSZK01000006.1_122</t>
         </is>
       </c>
       <c r="L90" t="n">
-        <v>316</v>
+        <v>39</v>
       </c>
       <c r="M90" t="inlineStr"/>
-      <c r="N90" t="inlineStr">
-        <is>
-          <t>ACP97_RS14700</t>
-        </is>
-      </c>
-      <c r="O90" t="inlineStr">
-        <is>
-          <t>WP_049998593.1</t>
-        </is>
-      </c>
-      <c r="P90" t="inlineStr">
-        <is>
-          <t>alkaline phosphatase family protein</t>
-        </is>
-      </c>
+      <c r="N90" t="inlineStr"/>
+      <c r="O90" t="inlineStr"/>
+      <c r="P90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Halococcus sediminicola</t>
+          <t>Halomarina oriensis</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>GCF_000755245.1</t>
+          <t>GCF_009791395.1</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -15155,39 +15133,55 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6</v>
+        <v>-5</v>
       </c>
       <c r="F91" t="b">
         <v>0</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>NZ_BBMP01000023.1</t>
+          <t>NZ_WSZK01000006.1</t>
         </is>
       </c>
       <c r="H91" t="n">
-        <v>88276</v>
+        <v>101934</v>
       </c>
       <c r="I91" t="n">
-        <v>88380</v>
+        <v>103157</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>NZ_BBMP01000023.1_89</t>
+          <t>NZ_WSZK01000006.1_121</t>
         </is>
       </c>
       <c r="L91" t="n">
-        <v>34</v>
-      </c>
-      <c r="M91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
-      <c r="O91" t="inlineStr"/>
-      <c r="P91" t="inlineStr"/>
+        <v>407</v>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>Acetyltransf_9 + Acetyltransf_17 + SCP2_2</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>GQS65_RS02370</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>WP_158203066.1</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>GNAT family N-acetyltransferase</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -15195,12 +15189,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Haloprofundus marisrubri</t>
+          <t>Halomarina oriensis</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>GCF_001469955.1</t>
+          <t>GCF_009791395.1</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -15209,21 +15203,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>-10</v>
+        <v>-4</v>
       </c>
       <c r="F92" t="b">
         <v>0</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>NZ_LOPU01000018.1</t>
+          <t>NZ_WSZK01000006.1</t>
         </is>
       </c>
       <c r="H92" t="n">
-        <v>127683</v>
+        <v>101433</v>
       </c>
       <c r="I92" t="n">
-        <v>128351</v>
+        <v>101855</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
@@ -15232,26 +15226,30 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>NZ_LOPU01000018.1_135</t>
+          <t>NZ_WSZK01000006.1_120</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>222</v>
-      </c>
-      <c r="M92" t="inlineStr"/>
+        <v>140</v>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>Luciferase</t>
+        </is>
+      </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>AUR64_RS06350</t>
+          <t>GQS65_RS02365</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>WP_155120539.1</t>
+          <t>WP_158203065.1</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>hypothetical protein</t>
+          <t>luciferase domain-containing protein</t>
         </is>
       </c>
     </row>
@@ -15261,12 +15259,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Haloprofundus marisrubri</t>
+          <t>Halomarina oriensis</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>GCF_001469955.1</t>
+          <t>GCF_009791395.1</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -15275,21 +15273,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>-9</v>
+        <v>-3</v>
       </c>
       <c r="F93" t="b">
         <v>0</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>NZ_LOPU01000018.1</t>
+          <t>NZ_WSZK01000006.1</t>
         </is>
       </c>
       <c r="H93" t="n">
-        <v>128387</v>
+        <v>100974</v>
       </c>
       <c r="I93" t="n">
-        <v>128671</v>
+        <v>101339</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
@@ -15298,30 +15296,26 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>NZ_LOPU01000018.1_136</t>
+          <t>NZ_WSZK01000006.1_119</t>
         </is>
       </c>
       <c r="L93" t="n">
-        <v>94</v>
-      </c>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>Ribosomal_L44</t>
-        </is>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="M93" t="inlineStr"/>
       <c r="N93" t="inlineStr">
         <is>
-          <t>AUR64_RS06355</t>
+          <t>GQS65_RS02360</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>WP_058581112.1</t>
+          <t>WP_233264983.1</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>50S ribosomal protein L44e</t>
+          <t>hypothetical protein</t>
         </is>
       </c>
     </row>
@@ -15331,12 +15325,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Haloprofundus marisrubri</t>
+          <t>Halomarina oriensis</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>GCF_001469955.1</t>
+          <t>GCF_009791395.1</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -15345,21 +15339,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>-8</v>
+        <v>-2</v>
       </c>
       <c r="F94" t="b">
         <v>0</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>NZ_LOPU01000018.1</t>
+          <t>NZ_WSZK01000006.1</t>
         </is>
       </c>
       <c r="H94" t="n">
-        <v>128676</v>
+        <v>100695</v>
       </c>
       <c r="I94" t="n">
-        <v>128849</v>
+        <v>100868</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
@@ -15368,7 +15362,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>NZ_LOPU01000018.1_137</t>
+          <t>NZ_WSZK01000006.1_118</t>
         </is>
       </c>
       <c r="L94" t="n">
@@ -15381,12 +15375,12 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>AUR64_RS06360</t>
+          <t>GQS65_RS02355</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>WP_058581113.1</t>
+          <t>WP_158203064.1</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
@@ -15401,12 +15395,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Haloprofundus marisrubri</t>
+          <t>Halomarina oriensis</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>GCF_001469955.1</t>
+          <t>GCF_009791395.1</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -15415,21 +15409,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>-7</v>
+        <v>-1</v>
       </c>
       <c r="F95" t="b">
         <v>0</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>NZ_LOPU01000018.1</t>
+          <t>NZ_WSZK01000006.1</t>
         </is>
       </c>
       <c r="H95" t="n">
-        <v>128865</v>
+        <v>100407</v>
       </c>
       <c r="I95" t="n">
-        <v>129665</v>
+        <v>100691</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
@@ -15438,30 +15432,30 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>NZ_LOPU01000018.1_138</t>
+          <t>NZ_WSZK01000006.1_117</t>
         </is>
       </c>
       <c r="L95" t="n">
-        <v>266</v>
+        <v>94</v>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>S1 + EIF_2_alpha</t>
+          <t>Ribosomal_L44</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>AUR64_RS06365</t>
+          <t>GQS65_RS02350</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>WP_058581114.1</t>
+          <t>WP_158203063.1</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>translation initiation factor IF-2 subunit alpha</t>
+          <t>50S ribosomal protein L44e</t>
         </is>
       </c>
     </row>
@@ -15471,12 +15465,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Haloprofundus marisrubri</t>
+          <t>Halomarina oriensis</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>GCF_001469955.1</t>
+          <t>GCF_009791395.1</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -15485,53 +15479,49 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="F96" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>NZ_LOPU01000018.1</t>
+          <t>NZ_WSZK01000006.1</t>
         </is>
       </c>
       <c r="H96" t="n">
-        <v>129662</v>
+        <v>99279</v>
       </c>
       <c r="I96" t="n">
-        <v>129844</v>
+        <v>100193</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>NZ_LOPU01000018.1_139</t>
+          <t>NZ_WSZK01000006.1_116</t>
         </is>
       </c>
       <c r="L96" t="n">
-        <v>60</v>
-      </c>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>Nop10p</t>
-        </is>
-      </c>
+        <v>304</v>
+      </c>
+      <c r="M96" t="inlineStr"/>
       <c r="N96" t="inlineStr">
         <is>
-          <t>AUR64_RS20005</t>
+          <t>GQS65_RS02345</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>WP_082230634.1</t>
+          <t>WP_158203062.1</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>RNA-protein complex protein Nop10</t>
+          <t>alpha/beta hydrolase</t>
         </is>
       </c>
     </row>
@@ -15541,12 +15531,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Haloprofundus marisrubri</t>
+          <t>Halomarina oriensis</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>GCF_001469955.1</t>
+          <t>GCF_009791395.1</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -15555,53 +15545,49 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>-5</v>
+        <v>1</v>
       </c>
       <c r="F97" t="b">
         <v>0</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>NZ_LOPU01000018.1</t>
+          <t>NZ_WSZK01000006.1</t>
         </is>
       </c>
       <c r="H97" t="n">
-        <v>129849</v>
+        <v>98920</v>
       </c>
       <c r="I97" t="n">
-        <v>130604</v>
+        <v>99186</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>NZ_LOPU01000018.1_140</t>
+          <t>NZ_WSZK01000006.1_115</t>
         </is>
       </c>
       <c r="L97" t="n">
-        <v>251</v>
-      </c>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>PAC2</t>
-        </is>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="M97" t="inlineStr"/>
       <c r="N97" t="inlineStr">
         <is>
-          <t>AUR64_RS06370</t>
+          <t>GQS65_RS02340</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>WP_058581115.1</t>
+          <t>WP_158203061.1</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>proteasome assembly chaperone family protein</t>
+          <t>HAH_0734 family protein</t>
         </is>
       </c>
     </row>
@@ -15611,12 +15597,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Haloprofundus marisrubri</t>
+          <t>Halomarina oriensis</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>GCF_001469955.1</t>
+          <t>GCF_009791395.1</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -15625,39 +15611,55 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>-4</v>
+        <v>2</v>
       </c>
       <c r="F98" t="b">
         <v>0</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>NZ_LOPU01000018.1</t>
+          <t>NZ_WSZK01000006.1</t>
         </is>
       </c>
       <c r="H98" t="n">
-        <v>130743</v>
+        <v>98077</v>
       </c>
       <c r="I98" t="n">
-        <v>130874</v>
+        <v>98718</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>NZ_LOPU01000018.1_141</t>
+          <t>NZ_WSZK01000006.1_114</t>
         </is>
       </c>
       <c r="L98" t="n">
-        <v>43</v>
-      </c>
-      <c r="M98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
-      <c r="O98" t="inlineStr"/>
-      <c r="P98" t="inlineStr"/>
+        <v>213</v>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>Copper-bind</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>GQS65_RS02335</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>WP_158203060.1</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>plastocyanin/azurin family copper-binding protein</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -15665,12 +15667,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Haloprofundus marisrubri</t>
+          <t>Halomarina oriensis</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>GCF_001469955.1</t>
+          <t>GCF_009791395.1</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -15679,49 +15681,53 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>-3</v>
+        <v>3</v>
       </c>
       <c r="F99" t="b">
         <v>0</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>NZ_LOPU01000018.1</t>
+          <t>NZ_WSZK01000006.1</t>
         </is>
       </c>
       <c r="H99" t="n">
-        <v>130880</v>
+        <v>97053</v>
       </c>
       <c r="I99" t="n">
-        <v>131173</v>
+        <v>97583</v>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>NZ_LOPU01000018.1_142</t>
+          <t>NZ_WSZK01000006.1_113</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>97</v>
-      </c>
-      <c r="M99" t="inlineStr"/>
+        <v>176</v>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>Polyketide_cyc2 + Polyketide_cyc</t>
+        </is>
+      </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>AUR64_RS06375</t>
+          <t>GQS65_RS02330</t>
         </is>
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>WP_058581116.1</t>
+          <t>WP_368279769.1</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>hypothetical protein</t>
+          <t>SRPBCC family protein</t>
         </is>
       </c>
     </row>
@@ -15731,12 +15737,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Haloprofundus marisrubri</t>
+          <t>Halomarina oriensis</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>GCF_001469955.1</t>
+          <t>GCF_009791395.1</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -15745,21 +15751,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>-2</v>
+        <v>4</v>
       </c>
       <c r="F100" t="b">
         <v>0</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>NZ_LOPU01000018.1</t>
+          <t>NZ_WSZK01000006.1</t>
         </is>
       </c>
       <c r="H100" t="n">
-        <v>131188</v>
+        <v>96186</v>
       </c>
       <c r="I100" t="n">
-        <v>131805</v>
+        <v>96950</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
@@ -15768,30 +15774,30 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>NZ_LOPU01000018.1_143</t>
+          <t>NZ_WSZK01000006.1_112</t>
         </is>
       </c>
       <c r="L100" t="n">
-        <v>205</v>
+        <v>254</v>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>DUF420</t>
+          <t>FAD_binding_2</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>AUR64_RS06380</t>
+          <t>GQS65_RS02325</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>WP_058581117.1</t>
+          <t>WP_158203059.1</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>DUF420 domain-containing protein</t>
+          <t>NAD(P)/FAD-dependent oxidoreductase</t>
         </is>
       </c>
     </row>
@@ -15801,12 +15807,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Haloprofundus marisrubri</t>
+          <t>Halomarina oriensis</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>GCF_001469955.1</t>
+          <t>GCF_009791395.1</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -15815,21 +15821,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F101" t="b">
         <v>0</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>NZ_LOPU01000018.1</t>
+          <t>NZ_WSZK01000006.1</t>
         </is>
       </c>
       <c r="H101" t="n">
-        <v>131896</v>
+        <v>94804</v>
       </c>
       <c r="I101" t="n">
-        <v>132942</v>
+        <v>95970</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
@@ -15838,30 +15844,30 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>NZ_LOPU01000018.1_144</t>
+          <t>NZ_WSZK01000006.1_111</t>
         </is>
       </c>
       <c r="L101" t="n">
-        <v>348</v>
+        <v>388</v>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Fe-ADH + Fe-ADH_2 + DHQ_synthase</t>
+          <t>Flavoprotein + DFP</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>AUR64_RS06385</t>
+          <t>GQS65_RS02320</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>WP_058581118.1</t>
+          <t>WP_158203122.1</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>NAD(P)-dependent glycerol-1-phosphate dehydrogenase</t>
+          <t>bifunctional phosphopantothenoylcysteine decarboxylase/phosphopantothenate--cysteine ligase CoaBC</t>
         </is>
       </c>
     </row>
@@ -15871,12 +15877,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Haloprofundus marisrubri</t>
+          <t>Halomarina oriensis</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>GCF_001469955.1</t>
+          <t>GCF_009791395.1</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -15885,21 +15891,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F102" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>NZ_LOPU01000018.1</t>
+          <t>NZ_WSZK01000006.1</t>
         </is>
       </c>
       <c r="H102" t="n">
-        <v>133145</v>
+        <v>94350</v>
       </c>
       <c r="I102" t="n">
-        <v>134038</v>
+        <v>94784</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
@@ -15908,26 +15914,30 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>NZ_LOPU01000018.1_145</t>
+          <t>NZ_WSZK01000006.1_110</t>
         </is>
       </c>
       <c r="L102" t="n">
-        <v>297</v>
-      </c>
-      <c r="M102" t="inlineStr"/>
+        <v>144</v>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>PhaG_MnhG_YufB</t>
+        </is>
+      </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>AUR64_RS06390</t>
+          <t>GQS65_RS02315</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>WP_058581119.1</t>
+          <t>WP_158203058.1</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>alpha/beta hydrolase</t>
+          <t>monovalent cation/H(+) antiporter subunit G</t>
         </is>
       </c>
     </row>
@@ -15937,12 +15947,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Haloprofundus marisrubri</t>
+          <t>Halomarina oriensis</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>GCF_001469955.1</t>
+          <t>GCF_009791395.1</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -15951,68 +15961,68 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F103" t="b">
         <v>0</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>NZ_LOPU01000018.1</t>
+          <t>NZ_WSZK01000006.1</t>
         </is>
       </c>
       <c r="H103" t="n">
-        <v>134041</v>
+        <v>94093</v>
       </c>
       <c r="I103" t="n">
-        <v>134715</v>
+        <v>94353</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>NZ_LOPU01000018.1_146</t>
+          <t>NZ_WSZK01000006.1_109</t>
         </is>
       </c>
       <c r="L103" t="n">
-        <v>224</v>
+        <v>86</v>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>LysE</t>
+          <t>MrpF_PhaF</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>AUR64_RS06395</t>
+          <t>GQS65_RS02310</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>WP_155120540.1</t>
+          <t>WP_158203121.1</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>LysE family translocator</t>
+          <t>monovalent cation/H+ antiporter complex subunit F</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Haloprofundus marisrubri</t>
+          <t>Haladaptatus paucihalophilus</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>GCF_001469955.1</t>
+          <t>GCF_000376445.1</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -16021,68 +16031,64 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>2</v>
+        <v>-9</v>
       </c>
       <c r="F104" t="b">
         <v>0</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>NZ_LOPU01000018.1</t>
+          <t>NZ_AQXI01000001.1</t>
         </is>
       </c>
       <c r="H104" t="n">
-        <v>134845</v>
+        <v>32337</v>
       </c>
       <c r="I104" t="n">
-        <v>135537</v>
+        <v>33278</v>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>NZ_LOPU01000018.1_147</t>
+          <t>NZ_AQXI01000001.1_42</t>
         </is>
       </c>
       <c r="L104" t="n">
-        <v>230</v>
-      </c>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>Fe_dep_repress + HTH_12 + MarR_2 + MarR + Fe_dep_repr_C + FeoA</t>
-        </is>
-      </c>
+        <v>313</v>
+      </c>
+      <c r="M104" t="inlineStr"/>
       <c r="N104" t="inlineStr">
         <is>
-          <t>AUR64_RS06400</t>
+          <t>B208_RS0100215</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>WP_058581120.1</t>
+          <t>WP_007978260.1</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>metal-dependent transcriptional regulator</t>
+          <t>archaeosortase A</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Haloprofundus marisrubri</t>
+          <t>Haladaptatus paucihalophilus</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>GCF_001469955.1</t>
+          <t>GCF_000376445.1</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -16091,21 +16097,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>3</v>
+        <v>-8</v>
       </c>
       <c r="F105" t="b">
         <v>0</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>NZ_LOPU01000018.1</t>
+          <t>NZ_AQXI01000001.1</t>
         </is>
       </c>
       <c r="H105" t="n">
-        <v>135590</v>
+        <v>31294</v>
       </c>
       <c r="I105" t="n">
-        <v>136912</v>
+        <v>32076</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
@@ -16114,45 +16120,45 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>NZ_LOPU01000018.1_148</t>
+          <t>NZ_AQXI01000001.1_41</t>
         </is>
       </c>
       <c r="L105" t="n">
-        <v>440</v>
+        <v>260</v>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>FAD_binding_3 + NAD_binding_8</t>
+          <t>HTH_24 + MarR_2 + MarR + HTH_IclR</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>AUR64_RS06405</t>
+          <t>B208_RS0100210</t>
         </is>
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>WP_058581831.1</t>
+          <t>WP_007978258.1</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>FAD-dependent oxidoreductase</t>
+          <t>DUF7839 domain-containing protein</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Haloprofundus marisrubri</t>
+          <t>Haladaptatus paucihalophilus</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>GCF_001469955.1</t>
+          <t>GCF_000376445.1</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -16161,68 +16167,68 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>4</v>
+        <v>-7</v>
       </c>
       <c r="F106" t="b">
         <v>0</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>NZ_LOPU01000018.1</t>
+          <t>NZ_AQXI01000001.1</t>
         </is>
       </c>
       <c r="H106" t="n">
-        <v>137043</v>
+        <v>30701</v>
       </c>
       <c r="I106" t="n">
-        <v>138236</v>
+        <v>31267</v>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>NZ_LOPU01000018.1_149</t>
+          <t>NZ_AQXI01000001.1_40</t>
         </is>
       </c>
       <c r="L106" t="n">
-        <v>397</v>
+        <v>188</v>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>PALP</t>
+          <t>DnaJ</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>AUR64_RS06410</t>
+          <t>B208_RS0100205</t>
         </is>
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>WP_058581121.1</t>
+          <t>WP_007978256.1</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>threonine synthase</t>
+          <t>J domain-containing protein</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Haloprofundus marisrubri</t>
+          <t>Haladaptatus paucihalophilus</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>GCF_001469955.1</t>
+          <t>GCF_000376445.1</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -16231,53 +16237,49 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5</v>
+        <v>-6</v>
       </c>
       <c r="F107" t="b">
         <v>0</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>NZ_LOPU01000018.1</t>
+          <t>NZ_AQXI01000001.1</t>
         </is>
       </c>
       <c r="H107" t="n">
-        <v>138369</v>
+        <v>29915</v>
       </c>
       <c r="I107" t="n">
-        <v>139655</v>
+        <v>30442</v>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>NZ_LOPU01000018.1_150</t>
+          <t>NZ_AQXI01000001.1_39</t>
         </is>
       </c>
       <c r="L107" t="n">
-        <v>428</v>
-      </c>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>FAD_binding_3 + FAD_binding_2 + NAD_binding_8 + Amino_oxidase</t>
-        </is>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="M107" t="inlineStr"/>
       <c r="N107" t="inlineStr">
         <is>
-          <t>AUR64_RS06415</t>
+          <t>B208_RS0100200</t>
         </is>
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>WP_058581122.1</t>
+          <t>WP_007978253.1</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>NAD(P)/FAD-dependent oxidoreductase</t>
+          <t>DUF7344 domain-containing protein</t>
         </is>
       </c>
     </row>
@@ -16287,12 +16289,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Halocatena sp023276375</t>
+          <t>Haladaptatus paucihalophilus</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>GCF_023276375.1</t>
+          <t>GCF_000376445.1</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -16301,53 +16303,53 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>-8</v>
+        <v>-5</v>
       </c>
       <c r="F108" t="b">
         <v>0</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>NZ_JALLPK010000001.1</t>
+          <t>NZ_AQXI01000001.1</t>
         </is>
       </c>
       <c r="H108" t="n">
-        <v>2725703</v>
+        <v>29135</v>
       </c>
       <c r="I108" t="n">
-        <v>2726368</v>
+        <v>29893</v>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>NZ_JALLPK010000001.1_2680</t>
+          <t>NZ_AQXI01000001.1_38</t>
         </is>
       </c>
       <c r="L108" t="n">
-        <v>221</v>
+        <v>252</v>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>LysE</t>
+          <t>PAC2</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>MW898_RS12610</t>
+          <t>B208_RS0100195</t>
         </is>
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>WP_368409092.1</t>
+          <t>WP_007978252.1</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>LysE family translocator</t>
+          <t>proteasome assembly chaperone family protein</t>
         </is>
       </c>
     </row>
@@ -16357,12 +16359,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Halocatena sp023276375</t>
+          <t>Haladaptatus paucihalophilus</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>GCF_023276375.1</t>
+          <t>GCF_000376445.1</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -16371,53 +16373,53 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>-7</v>
+        <v>-4</v>
       </c>
       <c r="F109" t="b">
         <v>0</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>NZ_JALLPK010000001.1</t>
+          <t>NZ_AQXI01000001.1</t>
         </is>
       </c>
       <c r="H109" t="n">
-        <v>2726495</v>
+        <v>28947</v>
       </c>
       <c r="I109" t="n">
-        <v>2727667</v>
+        <v>29129</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>NZ_JALLPK010000001.1_2681</t>
+          <t>NZ_AQXI01000001.1_37</t>
         </is>
       </c>
       <c r="L109" t="n">
-        <v>390</v>
+        <v>60</v>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>PALP</t>
+          <t>Nop10p</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>MW898_RS12615</t>
+          <t>B208_RS0100190</t>
         </is>
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>WP_248907824.1</t>
+          <t>WP_007978250.1</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>threonine synthase</t>
+          <t>RNA-protein complex protein Nop10</t>
         </is>
       </c>
     </row>
@@ -16427,12 +16429,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Halocatena sp023276375</t>
+          <t>Haladaptatus paucihalophilus</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>GCF_023276375.1</t>
+          <t>GCF_000376445.1</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -16441,53 +16443,53 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>-6</v>
+        <v>-3</v>
       </c>
       <c r="F110" t="b">
         <v>0</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>NZ_JALLPK010000001.1</t>
+          <t>NZ_AQXI01000001.1</t>
         </is>
       </c>
       <c r="H110" t="n">
-        <v>2727863</v>
+        <v>28150</v>
       </c>
       <c r="I110" t="n">
-        <v>2728456</v>
+        <v>28950</v>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>NZ_JALLPK010000001.1_2682</t>
+          <t>NZ_AQXI01000001.1_36</t>
         </is>
       </c>
       <c r="L110" t="n">
-        <v>197</v>
+        <v>266</v>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>DnaJ</t>
+          <t>S1 + EIF_2_alpha</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>MW898_RS12620</t>
+          <t>B208_RS0100185</t>
         </is>
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>WP_248907826.1</t>
+          <t>WP_007978248.1</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>J domain-containing protein</t>
+          <t>translation initiation factor IF-2 subunit alpha</t>
         </is>
       </c>
     </row>
@@ -16497,12 +16499,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Halocatena sp023276375</t>
+          <t>Haladaptatus paucihalophilus</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>GCF_023276375.1</t>
+          <t>GCF_000376445.1</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -16511,53 +16513,53 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="F111" t="b">
         <v>0</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>NZ_JALLPK010000001.1</t>
+          <t>NZ_AQXI01000001.1</t>
         </is>
       </c>
       <c r="H111" t="n">
-        <v>2728598</v>
+        <v>27980</v>
       </c>
       <c r="I111" t="n">
-        <v>2729386</v>
+        <v>28153</v>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>NZ_JALLPK010000001.1_2683</t>
+          <t>NZ_AQXI01000001.1_35</t>
         </is>
       </c>
       <c r="L111" t="n">
-        <v>262</v>
+        <v>57</v>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>PAC2</t>
+          <t>Ribosomal_S27e</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>MW898_RS12625</t>
+          <t>B208_RS0100180</t>
         </is>
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>WP_248907828.1</t>
+          <t>WP_007978247.1</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>proteasome assembly chaperone family protein</t>
+          <t>30S ribosomal protein S27e</t>
         </is>
       </c>
     </row>
@@ -16567,12 +16569,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Halocatena sp023276375</t>
+          <t>Haladaptatus paucihalophilus</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>GCF_023276375.1</t>
+          <t>GCF_000376445.1</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -16581,53 +16583,53 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="F112" t="b">
         <v>0</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>NZ_JALLPK010000001.1</t>
+          <t>NZ_AQXI01000001.1</t>
         </is>
       </c>
       <c r="H112" t="n">
-        <v>2729392</v>
+        <v>27790</v>
       </c>
       <c r="I112" t="n">
-        <v>2729574</v>
+        <v>27975</v>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>NZ_JALLPK010000001.1_2684</t>
+          <t>NZ_AQXI01000001.1_34</t>
         </is>
       </c>
       <c r="L112" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Nop10p</t>
+          <t>Ribosomal_L44</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>MW898_RS12630</t>
+          <t>B208_RS0100175</t>
         </is>
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>WP_248907837.1</t>
+          <t>WP_007978245.1</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>RNA-protein complex protein Nop10</t>
+          <t>50S ribosomal protein L44e</t>
         </is>
       </c>
     </row>
@@ -16637,12 +16639,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Halocatena sp023276375</t>
+          <t>Haladaptatus paucihalophilus</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>GCF_023276375.1</t>
+          <t>GCF_000376445.1</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -16651,21 +16653,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="F113" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>NZ_JALLPK010000001.1</t>
+          <t>NZ_AQXI01000001.1</t>
         </is>
       </c>
       <c r="H113" t="n">
-        <v>2729606</v>
+        <v>26622</v>
       </c>
       <c r="I113" t="n">
-        <v>2730406</v>
+        <v>27524</v>
       </c>
       <c r="J113" t="inlineStr">
         <is>
@@ -16674,30 +16676,26 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>NZ_JALLPK010000001.1_2685</t>
+          <t>NZ_AQXI01000001.1_33</t>
         </is>
       </c>
       <c r="L113" t="n">
-        <v>266</v>
-      </c>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>S1 + EIF_2_alpha</t>
-        </is>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="M113" t="inlineStr"/>
       <c r="N113" t="inlineStr">
         <is>
-          <t>MW898_RS12635</t>
+          <t>B208_RS0100170</t>
         </is>
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>WP_248907839.1</t>
+          <t>WP_049805627.1</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>translation initiation factor IF-2 subunit alpha</t>
+          <t>hypothetical protein</t>
         </is>
       </c>
     </row>
@@ -16707,12 +16705,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Halocatena sp023276375</t>
+          <t>Haladaptatus paucihalophilus</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>GCF_023276375.1</t>
+          <t>GCF_000376445.1</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -16721,21 +16719,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="F114" t="b">
         <v>0</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>NZ_JALLPK010000001.1</t>
+          <t>NZ_AQXI01000001.1</t>
         </is>
       </c>
       <c r="H114" t="n">
-        <v>2730568</v>
+        <v>25711</v>
       </c>
       <c r="I114" t="n">
-        <v>2730753</v>
+        <v>26610</v>
       </c>
       <c r="J114" t="inlineStr">
         <is>
@@ -16744,30 +16742,30 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>NZ_JALLPK010000001.1_2686</t>
+          <t>NZ_AQXI01000001.1_32</t>
         </is>
       </c>
       <c r="L114" t="n">
-        <v>61</v>
+        <v>299</v>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Ribosomal_S27e</t>
+          <t>DUF900</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>MW898_RS12640</t>
+          <t>B208_RS0100165</t>
         </is>
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>WP_248907841.1</t>
+          <t>WP_007978241.1</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>30S ribosomal protein S27e</t>
+          <t>alpha/beta hydrolase</t>
         </is>
       </c>
     </row>
@@ -16777,12 +16775,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Halocatena sp023276375</t>
+          <t>Haladaptatus paucihalophilus</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>GCF_023276375.1</t>
+          <t>GCF_000376445.1</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -16791,21 +16789,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="F115" t="b">
         <v>0</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>NZ_JALLPK010000001.1</t>
+          <t>NZ_AQXI01000001.1</t>
         </is>
       </c>
       <c r="H115" t="n">
-        <v>2730756</v>
+        <v>25349</v>
       </c>
       <c r="I115" t="n">
-        <v>2731040</v>
+        <v>25618</v>
       </c>
       <c r="J115" t="inlineStr">
         <is>
@@ -16814,30 +16812,26 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>NZ_JALLPK010000001.1_2687</t>
+          <t>NZ_AQXI01000001.1_31</t>
         </is>
       </c>
       <c r="L115" t="n">
-        <v>94</v>
-      </c>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>Ribosomal_L44</t>
-        </is>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="M115" t="inlineStr"/>
       <c r="N115" t="inlineStr">
         <is>
-          <t>MW898_RS12645</t>
+          <t>B208_RS0100160</t>
         </is>
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>WP_248907843.1</t>
+          <t>WP_007978239.1</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>50S ribosomal protein L44e</t>
+          <t>HAH_0734 family protein</t>
         </is>
       </c>
     </row>
@@ -16847,12 +16841,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Halocatena sp023276375</t>
+          <t>Haladaptatus paucihalophilus</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>GCF_023276375.1</t>
+          <t>GCF_000376445.1</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -16861,49 +16855,53 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F116" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>NZ_JALLPK010000001.1</t>
+          <t>NZ_AQXI01000001.1</t>
         </is>
       </c>
       <c r="H116" t="n">
-        <v>2731297</v>
+        <v>23821</v>
       </c>
       <c r="I116" t="n">
-        <v>2732199</v>
+        <v>24987</v>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>NZ_JALLPK010000001.1_2688</t>
+          <t>NZ_AQXI01000001.1_30</t>
         </is>
       </c>
       <c r="L116" t="n">
-        <v>300</v>
-      </c>
-      <c r="M116" t="inlineStr"/>
+        <v>388</v>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>Thiolase_N + ketoacyl-synt + Thiolase_C_1 + Thiolase_C</t>
+        </is>
+      </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>MW898_RS12650</t>
+          <t>B208_RS0100155</t>
         </is>
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>WP_248907845.1</t>
+          <t>WP_007978238.1</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>hypothetical protein</t>
+          <t>thiolase domain-containing protein</t>
         </is>
       </c>
     </row>
@@ -16913,12 +16911,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Halocatena sp023276375</t>
+          <t>Haladaptatus paucihalophilus</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>GCF_023276375.1</t>
+          <t>GCF_000376445.1</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -16927,21 +16925,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F117" t="b">
         <v>0</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>NZ_JALLPK010000001.1</t>
+          <t>NZ_AQXI01000001.1</t>
         </is>
       </c>
       <c r="H117" t="n">
-        <v>2732202</v>
+        <v>23447</v>
       </c>
       <c r="I117" t="n">
-        <v>2733191</v>
+        <v>23824</v>
       </c>
       <c r="J117" t="inlineStr">
         <is>
@@ -16950,30 +16948,30 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>NZ_JALLPK010000001.1_2689</t>
+          <t>NZ_AQXI01000001.1_29</t>
         </is>
       </c>
       <c r="L117" t="n">
-        <v>329</v>
+        <v>125</v>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>OCD_Mu_crystall</t>
+          <t>OB_aCoA_assoc</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>MW898_RS12655</t>
+          <t>B208_RS0100150</t>
         </is>
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>WP_248907846.1</t>
+          <t>WP_007978236.1</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>ornithine cyclodeaminase family protein</t>
+          <t>Zn-ribbon domain-containing OB-fold protein</t>
         </is>
       </c>
     </row>
@@ -16983,12 +16981,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Halocatena sp023276375</t>
+          <t>Haladaptatus paucihalophilus</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>GCF_023276375.1</t>
+          <t>GCF_000376445.1</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -16997,49 +16995,53 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F118" t="b">
         <v>0</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>NZ_JALLPK010000001.1</t>
+          <t>NZ_AQXI01000001.1</t>
         </is>
       </c>
       <c r="H118" t="n">
-        <v>2733246</v>
+        <v>22532</v>
       </c>
       <c r="I118" t="n">
-        <v>2733473</v>
+        <v>23470</v>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>NZ_JALLPK010000001.1_2690</t>
+          <t>NZ_AQXI01000001.1_28</t>
         </is>
       </c>
       <c r="L118" t="n">
-        <v>75</v>
-      </c>
-      <c r="M118" t="inlineStr"/>
+        <v>312</v>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>Abhydrolase_1 + Abhydrolase_6</t>
+        </is>
+      </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>MW898_RS12660</t>
+          <t>B208_RS0100145</t>
         </is>
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>WP_248907848.1</t>
+          <t>WP_007978234.1</t>
         </is>
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>DUF8015 family protein</t>
+          <t>alpha/beta fold hydrolase</t>
         </is>
       </c>
     </row>
@@ -17049,12 +17051,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Halocatena sp023276375</t>
+          <t>Haladaptatus paucihalophilus</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>GCF_023276375.1</t>
+          <t>GCF_000376445.1</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -17063,21 +17065,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F119" t="b">
         <v>0</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>NZ_JALLPK010000001.1</t>
+          <t>NZ_AQXI01000001.1</t>
         </is>
       </c>
       <c r="H119" t="n">
-        <v>2734018</v>
+        <v>21816</v>
       </c>
       <c r="I119" t="n">
-        <v>2735277</v>
+        <v>22487</v>
       </c>
       <c r="J119" t="inlineStr">
         <is>
@@ -17086,45 +17088,41 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>NZ_JALLPK010000001.1_2691</t>
+          <t>NZ_AQXI01000001.1_27</t>
         </is>
       </c>
       <c r="L119" t="n">
-        <v>419</v>
+        <v>223</v>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>MFS_1</t>
+          <t>MeaB</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>MW898_RS12665</t>
-        </is>
-      </c>
-      <c r="O119" t="inlineStr">
-        <is>
-          <t>WP_248907850.1</t>
-        </is>
-      </c>
+          <t>B208_RS0100140</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>MFS transporter</t>
+          <t>methylmalonyl Co-A mutase-associated GTPase MeaB</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Halocatena sp023276375</t>
+          <t>Halorussus sp024138125</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>GCF_023276375.1</t>
+          <t>GCF_024138125.1</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -17133,68 +17131,68 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>4</v>
+        <v>-10</v>
       </c>
       <c r="F120" t="b">
         <v>0</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>NZ_JALLPK010000001.1</t>
+          <t>NZ_CP099993.1</t>
         </is>
       </c>
       <c r="H120" t="n">
-        <v>2735298</v>
+        <v>935201</v>
       </c>
       <c r="I120" t="n">
-        <v>2735843</v>
+        <v>935983</v>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>NZ_JALLPK010000001.1_2692</t>
+          <t>NZ_CP099993.1_949</t>
         </is>
       </c>
       <c r="L120" t="n">
-        <v>181</v>
+        <v>260</v>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>DUF3054</t>
+          <t>HTH_24 + HTH_20 + MarR + MarR_2 + HTH_5 + HTH_27 + HTH_IclR</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>MW898_RS12670</t>
+          <t>NGM10_RS04755</t>
         </is>
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>WP_248907851.1</t>
+          <t>WP_253482358.1</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>DUF3054 domain-containing protein</t>
+          <t>DUF7839 domain-containing protein</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Halocatena sp023276375</t>
+          <t>Halorussus sp024138125</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>GCF_023276375.1</t>
+          <t>GCF_024138125.1</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -17203,68 +17201,68 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>5</v>
+        <v>-9</v>
       </c>
       <c r="F121" t="b">
         <v>0</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>NZ_JALLPK010000001.1</t>
+          <t>NZ_CP099993.1</t>
         </is>
       </c>
       <c r="H121" t="n">
-        <v>2735849</v>
+        <v>935976</v>
       </c>
       <c r="I121" t="n">
-        <v>2736379</v>
+        <v>936635</v>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>NZ_JALLPK010000001.1_2693</t>
+          <t>NZ_CP099993.1_950</t>
         </is>
       </c>
       <c r="L121" t="n">
-        <v>176</v>
+        <v>219</v>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Acetyltransf_1</t>
+          <t>DnaJ</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>MW898_RS12675</t>
+          <t>NGM10_RS04760</t>
         </is>
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>WP_248907853.1</t>
+          <t>WP_253483764.1</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>GNAT family N-acetyltransferase</t>
+          <t>J domain-containing protein</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Halocatena sp023276375</t>
+          <t>Halorussus sp024138125</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>GCF_023276375.1</t>
+          <t>GCF_024138125.1</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -17273,21 +17271,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6</v>
+        <v>-8</v>
       </c>
       <c r="F122" t="b">
         <v>0</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>NZ_JALLPK010000001.1</t>
+          <t>NZ_CP099993.1</t>
         </is>
       </c>
       <c r="H122" t="n">
-        <v>2736406</v>
+        <v>936689</v>
       </c>
       <c r="I122" t="n">
-        <v>2737380</v>
+        <v>937225</v>
       </c>
       <c r="J122" t="inlineStr">
         <is>
@@ -17296,30 +17294,26 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>NZ_JALLPK010000001.1_2694</t>
+          <t>NZ_CP099993.1_951</t>
         </is>
       </c>
       <c r="L122" t="n">
-        <v>324</v>
-      </c>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>XPG_N + XPG_I</t>
-        </is>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="M122" t="inlineStr"/>
       <c r="N122" t="inlineStr">
         <is>
-          <t>MW898_RS12680</t>
+          <t>NGM10_RS04765</t>
         </is>
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>WP_248907855.1</t>
+          <t>WP_253482360.1</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>flap endonuclease-1</t>
+          <t>DUF7344 domain-containing protein</t>
         </is>
       </c>
     </row>
@@ -17329,12 +17323,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Halomarina oriensis</t>
+          <t>Halorussus sp024138125</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>GCF_009791395.1</t>
+          <t>GCF_024138125.1</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -17343,21 +17337,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="F123" t="b">
         <v>0</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>NZ_WSZK01000006.1</t>
+          <t>NZ_CP099993.1</t>
         </is>
       </c>
       <c r="H123" t="n">
-        <v>104745</v>
+        <v>937258</v>
       </c>
       <c r="I123" t="n">
-        <v>105908</v>
+        <v>938016</v>
       </c>
       <c r="J123" t="inlineStr">
         <is>
@@ -17366,26 +17360,30 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>NZ_WSZK01000006.1_124</t>
+          <t>NZ_CP099993.1_952</t>
         </is>
       </c>
       <c r="L123" t="n">
-        <v>387</v>
-      </c>
-      <c r="M123" t="inlineStr"/>
+        <v>252</v>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>PAC2</t>
+        </is>
+      </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>GQS65_RS02380</t>
+          <t>NGM10_RS04770</t>
         </is>
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>WP_158203068.1</t>
+          <t>WP_253482362.1</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>hypothetical protein</t>
+          <t>proteasome assembly chaperone family protein</t>
         </is>
       </c>
     </row>
@@ -17395,12 +17393,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Halomarina oriensis</t>
+          <t>Halorussus sp024138125</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>GCF_009791395.1</t>
+          <t>GCF_024138125.1</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -17409,21 +17407,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="F124" t="b">
         <v>0</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>NZ_WSZK01000006.1</t>
+          <t>NZ_CP099993.1</t>
         </is>
       </c>
       <c r="H124" t="n">
-        <v>103404</v>
+        <v>938022</v>
       </c>
       <c r="I124" t="n">
-        <v>104561</v>
+        <v>938204</v>
       </c>
       <c r="J124" t="inlineStr">
         <is>
@@ -17432,30 +17430,30 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>NZ_WSZK01000006.1_123</t>
+          <t>NZ_CP099993.1_953</t>
         </is>
       </c>
       <c r="L124" t="n">
-        <v>385</v>
+        <v>60</v>
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Acyl-CoA_dh_N + Acyl-CoA_dh_M + Acyl-CoA_dh_1 + Acyl-CoA_dh_2</t>
+          <t>Nop10p</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>GQS65_RS02375</t>
+          <t>NGM10_RS04775</t>
         </is>
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>WP_158203067.1</t>
+          <t>WP_253482363.1</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>acyl-CoA dehydrogenase family protein</t>
+          <t>RNA-protein complex protein Nop10</t>
         </is>
       </c>
     </row>
@@ -17465,12 +17463,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Halomarina oriensis</t>
+          <t>Halorussus sp024138125</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>GCF_009791395.1</t>
+          <t>GCF_024138125.1</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -17479,21 +17477,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="F125" t="b">
         <v>0</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>NZ_WSZK01000006.1</t>
+          <t>NZ_CP099993.1</t>
         </is>
       </c>
       <c r="H125" t="n">
-        <v>103204</v>
+        <v>938209</v>
       </c>
       <c r="I125" t="n">
-        <v>103323</v>
+        <v>939009</v>
       </c>
       <c r="J125" t="inlineStr">
         <is>
@@ -17502,16 +17500,32 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>NZ_WSZK01000006.1_122</t>
+          <t>NZ_CP099993.1_954</t>
         </is>
       </c>
       <c r="L125" t="n">
-        <v>39</v>
-      </c>
-      <c r="M125" t="inlineStr"/>
-      <c r="N125" t="inlineStr"/>
-      <c r="O125" t="inlineStr"/>
-      <c r="P125" t="inlineStr"/>
+        <v>266</v>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>S1 + EIF_2_alpha</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>NGM10_RS04780</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>WP_253482364.1</t>
+        </is>
+      </c>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>translation initiation factor IF-2 subunit alpha</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -17519,12 +17533,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Halomarina oriensis</t>
+          <t>Halorussus sp024138125</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>GCF_009791395.1</t>
+          <t>GCF_024138125.1</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -17533,53 +17547,53 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="F126" t="b">
         <v>0</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>NZ_WSZK01000006.1</t>
+          <t>NZ_CP099993.1</t>
         </is>
       </c>
       <c r="H126" t="n">
-        <v>101934</v>
+        <v>939006</v>
       </c>
       <c r="I126" t="n">
-        <v>103157</v>
+        <v>939179</v>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>NZ_WSZK01000006.1_121</t>
+          <t>NZ_CP099993.1_955</t>
         </is>
       </c>
       <c r="L126" t="n">
-        <v>407</v>
+        <v>57</v>
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Acetyltransf_9 + Acetyltransf_17 + SCP2_2</t>
+          <t>Ribosomal_S27e</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>GQS65_RS02370</t>
+          <t>NGM10_RS04785</t>
         </is>
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>WP_158203066.1</t>
+          <t>WP_253482365.1</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>GNAT family N-acetyltransferase</t>
+          <t>30S ribosomal protein S27e</t>
         </is>
       </c>
     </row>
@@ -17589,12 +17603,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Halomarina oriensis</t>
+          <t>Halorussus sp024138125</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>GCF_009791395.1</t>
+          <t>GCF_024138125.1</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -17603,53 +17617,53 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="F127" t="b">
         <v>0</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>NZ_WSZK01000006.1</t>
+          <t>NZ_CP099993.1</t>
         </is>
       </c>
       <c r="H127" t="n">
-        <v>101433</v>
+        <v>939184</v>
       </c>
       <c r="I127" t="n">
-        <v>101855</v>
+        <v>939459</v>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>NZ_WSZK01000006.1_120</t>
+          <t>NZ_CP099993.1_956</t>
         </is>
       </c>
       <c r="L127" t="n">
-        <v>140</v>
+        <v>91</v>
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Luciferase</t>
+          <t>Ribosomal_L44</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>GQS65_RS02365</t>
+          <t>NGM10_RS04790</t>
         </is>
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>WP_158203065.1</t>
+          <t>WP_128477830.1</t>
         </is>
       </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>luciferase domain-containing protein</t>
+          <t>50S ribosomal protein L44e</t>
         </is>
       </c>
     </row>
@@ -17659,12 +17673,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Halomarina oriensis</t>
+          <t>Halorussus sp024138125</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>GCF_009791395.1</t>
+          <t>GCF_024138125.1</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -17673,44 +17687,38 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="F128" t="b">
         <v>0</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>NZ_WSZK01000006.1</t>
+          <t>NZ_CP099993.1</t>
         </is>
       </c>
       <c r="H128" t="n">
-        <v>100974</v>
+        <v>939791</v>
       </c>
       <c r="I128" t="n">
-        <v>101339</v>
+        <v>940027</v>
       </c>
       <c r="J128" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t>NZ_WSZK01000006.1_119</t>
-        </is>
-      </c>
-      <c r="L128" t="n">
-        <v>121</v>
-      </c>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
       <c r="M128" t="inlineStr"/>
       <c r="N128" t="inlineStr">
         <is>
-          <t>GQS65_RS02360</t>
+          <t>NGM10_RS04795</t>
         </is>
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>WP_233264983.1</t>
+          <t>WP_253482366.1</t>
         </is>
       </c>
       <c r="P128" t="inlineStr">
@@ -17725,12 +17733,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Halomarina oriensis</t>
+          <t>Halorussus sp024138125</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>GCF_009791395.1</t>
+          <t>GCF_024138125.1</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -17739,21 +17747,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="F129" t="b">
         <v>0</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>NZ_WSZK01000006.1</t>
+          <t>NZ_CP099993.1</t>
         </is>
       </c>
       <c r="H129" t="n">
-        <v>100695</v>
+        <v>940028</v>
       </c>
       <c r="I129" t="n">
-        <v>100868</v>
+        <v>940432</v>
       </c>
       <c r="J129" t="inlineStr">
         <is>
@@ -17762,30 +17770,26 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>NZ_WSZK01000006.1_118</t>
+          <t>NZ_CP099993.1_957</t>
         </is>
       </c>
       <c r="L129" t="n">
-        <v>57</v>
-      </c>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>Ribosomal_S27e</t>
-        </is>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="M129" t="inlineStr"/>
       <c r="N129" t="inlineStr">
         <is>
-          <t>GQS65_RS02355</t>
+          <t>NGM10_RS04800</t>
         </is>
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>WP_158203064.1</t>
+          <t>WP_253482367.1</t>
         </is>
       </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>30S ribosomal protein S27e</t>
+          <t>hypothetical protein</t>
         </is>
       </c>
     </row>
@@ -17795,12 +17799,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Halomarina oriensis</t>
+          <t>Halorussus sp024138125</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>GCF_009791395.1</t>
+          <t>GCF_024138125.1</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -17809,21 +17813,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="F130" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>NZ_WSZK01000006.1</t>
+          <t>NZ_CP099993.1</t>
         </is>
       </c>
       <c r="H130" t="n">
-        <v>100407</v>
+        <v>940489</v>
       </c>
       <c r="I130" t="n">
-        <v>100691</v>
+        <v>941391</v>
       </c>
       <c r="J130" t="inlineStr">
         <is>
@@ -17832,30 +17836,30 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>NZ_WSZK01000006.1_117</t>
+          <t>NZ_CP099993.1_958</t>
         </is>
       </c>
       <c r="L130" t="n">
-        <v>94</v>
+        <v>300</v>
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Ribosomal_L44</t>
+          <t>DUF900</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>GQS65_RS02350</t>
+          <t>NGM10_RS04805</t>
         </is>
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>WP_158203063.1</t>
+          <t>WP_253482368.1</t>
         </is>
       </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>50S ribosomal protein L44e</t>
+          <t>alpha/beta hydrolase</t>
         </is>
       </c>
     </row>
@@ -17865,12 +17869,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Halomarina oriensis</t>
+          <t>Halorussus sp024138125</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>GCF_009791395.1</t>
+          <t>GCF_024138125.1</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -17879,49 +17883,49 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F131" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>NZ_WSZK01000006.1</t>
+          <t>NZ_CP099993.1</t>
         </is>
       </c>
       <c r="H131" t="n">
-        <v>99279</v>
+        <v>941464</v>
       </c>
       <c r="I131" t="n">
-        <v>100193</v>
+        <v>941733</v>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>NZ_WSZK01000006.1_116</t>
+          <t>NZ_CP099993.1_959</t>
         </is>
       </c>
       <c r="L131" t="n">
-        <v>304</v>
+        <v>89</v>
       </c>
       <c r="M131" t="inlineStr"/>
       <c r="N131" t="inlineStr">
         <is>
-          <t>GQS65_RS02345</t>
+          <t>NGM10_RS04810</t>
         </is>
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>WP_158203062.1</t>
+          <t>WP_253482369.1</t>
         </is>
       </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>alpha/beta hydrolase</t>
+          <t>HAH_0734 family protein</t>
         </is>
       </c>
     </row>
@@ -17931,12 +17935,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Halomarina oriensis</t>
+          <t>Halorussus sp024138125</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>GCF_009791395.1</t>
+          <t>GCF_024138125.1</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -17945,21 +17949,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F132" t="b">
         <v>0</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>NZ_WSZK01000006.1</t>
+          <t>NZ_CP099993.1</t>
         </is>
       </c>
       <c r="H132" t="n">
-        <v>98920</v>
+        <v>941756</v>
       </c>
       <c r="I132" t="n">
-        <v>99186</v>
+        <v>941971</v>
       </c>
       <c r="J132" t="inlineStr">
         <is>
@@ -17968,26 +17972,26 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>NZ_WSZK01000006.1_115</t>
+          <t>NZ_CP099993.1_960</t>
         </is>
       </c>
       <c r="L132" t="n">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="M132" t="inlineStr"/>
       <c r="N132" t="inlineStr">
         <is>
-          <t>GQS65_RS02340</t>
+          <t>NGM10_RS18345</t>
         </is>
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>WP_158203061.1</t>
+          <t>WP_253482371.1</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>HAH_0734 family protein</t>
+          <t>hypothetical protein</t>
         </is>
       </c>
     </row>
@@ -17997,12 +18001,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Halomarina oriensis</t>
+          <t>Halorussus sp024138125</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>GCF_009791395.1</t>
+          <t>GCF_024138125.1</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -18011,21 +18015,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F133" t="b">
         <v>0</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>NZ_WSZK01000006.1</t>
+          <t>NZ_CP099993.1</t>
         </is>
       </c>
       <c r="H133" t="n">
-        <v>98077</v>
+        <v>942022</v>
       </c>
       <c r="I133" t="n">
-        <v>98718</v>
+        <v>943314</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
@@ -18034,30 +18038,30 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>NZ_WSZK01000006.1_114</t>
+          <t>NZ_CP099993.1_961</t>
         </is>
       </c>
       <c r="L133" t="n">
-        <v>213</v>
+        <v>430</v>
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Copper-bind</t>
+          <t>MFS_1</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>GQS65_RS02335</t>
+          <t>NGM10_RS04820</t>
         </is>
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>WP_158203060.1</t>
+          <t>WP_368408655.1</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>plastocyanin/azurin family copper-binding protein</t>
+          <t>MFS transporter</t>
         </is>
       </c>
     </row>
@@ -18067,12 +18071,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Halomarina oriensis</t>
+          <t>Halorussus sp024138125</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>GCF_009791395.1</t>
+          <t>GCF_024138125.1</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -18081,53 +18085,49 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F134" t="b">
         <v>0</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>NZ_WSZK01000006.1</t>
+          <t>NZ_CP099993.1</t>
         </is>
       </c>
       <c r="H134" t="n">
-        <v>97053</v>
+        <v>943440</v>
       </c>
       <c r="I134" t="n">
-        <v>97583</v>
+        <v>943835</v>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>NZ_WSZK01000006.1_113</t>
+          <t>NZ_CP099993.1_962</t>
         </is>
       </c>
       <c r="L134" t="n">
-        <v>176</v>
-      </c>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>Polyketide_cyc2 + Polyketide_cyc</t>
-        </is>
-      </c>
+        <v>131</v>
+      </c>
+      <c r="M134" t="inlineStr"/>
       <c r="N134" t="inlineStr">
         <is>
-          <t>GQS65_RS02330</t>
+          <t>NGM10_RS04825</t>
         </is>
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>WP_368279769.1</t>
+          <t>WP_253482374.1</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>SRPBCC family protein</t>
+          <t>hypothetical protein</t>
         </is>
       </c>
     </row>
@@ -18137,12 +18137,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Halomarina oriensis</t>
+          <t>Halorussus sp024138125</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>GCF_009791395.1</t>
+          <t>GCF_024138125.1</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -18151,53 +18151,53 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F135" t="b">
         <v>0</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>NZ_WSZK01000006.1</t>
+          <t>NZ_CP099993.1</t>
         </is>
       </c>
       <c r="H135" t="n">
-        <v>96186</v>
+        <v>944171</v>
       </c>
       <c r="I135" t="n">
-        <v>96950</v>
+        <v>944677</v>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>NZ_WSZK01000006.1_112</t>
+          <t>NZ_CP099993.1_963</t>
         </is>
       </c>
       <c r="L135" t="n">
-        <v>254</v>
+        <v>168</v>
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>FAD_binding_2</t>
+          <t>CinA</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>GQS65_RS02325</t>
+          <t>NGM10_RS04830</t>
         </is>
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t>WP_158203059.1</t>
+          <t>WP_253482376.1</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>NAD(P)/FAD-dependent oxidoreductase</t>
+          <t>CinA family protein</t>
         </is>
       </c>
     </row>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Halomarina oriensis</t>
+          <t>Halorussus sp024138125</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>GCF_009791395.1</t>
+          <t>GCF_024138125.1</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -18221,53 +18221,53 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F136" t="b">
         <v>0</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>NZ_WSZK01000006.1</t>
+          <t>NZ_CP099993.1</t>
         </is>
       </c>
       <c r="H136" t="n">
-        <v>94804</v>
+        <v>944755</v>
       </c>
       <c r="I136" t="n">
-        <v>95970</v>
+        <v>945243</v>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>NZ_WSZK01000006.1_111</t>
+          <t>NZ_CP099993.1_964</t>
         </is>
       </c>
       <c r="L136" t="n">
-        <v>388</v>
+        <v>162</v>
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Flavoprotein + DFP</t>
+          <t>YdjM</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>GQS65_RS02320</t>
+          <t>NGM10_RS04835</t>
         </is>
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>WP_158203122.1</t>
+          <t>WP_253482379.1</t>
         </is>
       </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>bifunctional phosphopantothenoylcysteine decarboxylase/phosphopantothenate--cysteine ligase CoaBC</t>
+          <t>metal-dependent hydrolase</t>
         </is>
       </c>
     </row>
@@ -18277,12 +18277,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Halomarina oriensis</t>
+          <t>Halorussus sp024138125</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>GCF_009791395.1</t>
+          <t>GCF_024138125.1</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -18291,53 +18291,53 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F137" t="b">
         <v>0</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>NZ_WSZK01000006.1</t>
+          <t>NZ_CP099993.1</t>
         </is>
       </c>
       <c r="H137" t="n">
-        <v>94350</v>
+        <v>945240</v>
       </c>
       <c r="I137" t="n">
-        <v>94784</v>
+        <v>945995</v>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>NZ_WSZK01000006.1_110</t>
+          <t>NZ_CP099993.1_965</t>
         </is>
       </c>
       <c r="L137" t="n">
-        <v>144</v>
+        <v>251</v>
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>PhaG_MnhG_YufB</t>
+          <t>PHP_C</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>GQS65_RS02315</t>
+          <t>NGM10_RS04840</t>
         </is>
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>WP_158203058.1</t>
+          <t>WP_253482381.1</t>
         </is>
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>monovalent cation/H(+) antiporter subunit G</t>
+          <t>PHP domain-containing protein</t>
         </is>
       </c>
     </row>
@@ -18347,12 +18347,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Halomarina oriensis</t>
+          <t>Halorussus sp024138125</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>GCF_009791395.1</t>
+          <t>GCF_024138125.1</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -18361,21 +18361,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F138" t="b">
         <v>0</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>NZ_WSZK01000006.1</t>
+          <t>NZ_CP099993.1</t>
         </is>
       </c>
       <c r="H138" t="n">
-        <v>94093</v>
+        <v>946138</v>
       </c>
       <c r="I138" t="n">
-        <v>94353</v>
+        <v>946782</v>
       </c>
       <c r="J138" t="inlineStr">
         <is>
@@ -18384,30 +18384,30 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>NZ_WSZK01000006.1_109</t>
+          <t>NZ_CP099993.1_966</t>
         </is>
       </c>
       <c r="L138" t="n">
-        <v>86</v>
+        <v>214</v>
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>MrpF_PhaF</t>
+          <t>Hydrolase + HAD + HAD_2 + Hydrolase_like</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>GQS65_RS02310</t>
+          <t>NGM10_RS04845</t>
         </is>
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t>WP_158203121.1</t>
+          <t>WP_253482383.1</t>
         </is>
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>monovalent cation/H+ antiporter complex subunit F</t>
+          <t>HAD family hydrolase</t>
         </is>
       </c>
     </row>
@@ -18417,67 +18417,67 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Halalkalicoccus sp022561895</t>
+          <t>Haloarchaeobius iranensis</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>GCA_022561895.1</t>
+          <t>GCF_900103505.1</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>GenBank</t>
+          <t>RefSeq</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="F139" t="b">
         <v>0</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>JADFQH010000144.1</t>
+          <t>NZ_FNIA01000003.1</t>
         </is>
       </c>
       <c r="H139" t="n">
-        <v>3</v>
+        <v>157195</v>
       </c>
       <c r="I139" t="n">
-        <v>281</v>
+        <v>157881</v>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>JADFQH010000144.1_1</t>
+          <t>NZ_FNIA01000003.1_168</t>
         </is>
       </c>
       <c r="L139" t="n">
-        <v>92</v>
+        <v>228</v>
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>HbpS-like</t>
+          <t>DUF3267</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>IH933_10420</t>
+          <t>BLT27_RS03625</t>
         </is>
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t>MCH7660962.1</t>
+          <t>WP_089731671.1</t>
         </is>
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>heme-binding protein</t>
+          <t>DUF3267 domain-containing protein</t>
         </is>
       </c>
     </row>
@@ -18487,67 +18487,67 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Halalkalicoccus sp022561895</t>
+          <t>Haloarchaeobius iranensis</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>GCA_022561895.1</t>
+          <t>GCF_900103505.1</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>GenBank</t>
+          <t>RefSeq</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>-2</v>
+        <v>-6</v>
       </c>
       <c r="F140" t="b">
         <v>0</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>JADFQH010000144.1</t>
+          <t>NZ_FNIA01000003.1</t>
         </is>
       </c>
       <c r="H140" t="n">
-        <v>370</v>
+        <v>156393</v>
       </c>
       <c r="I140" t="n">
-        <v>1368</v>
+        <v>157136</v>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>JADFQH010000144.1_2</t>
+          <t>NZ_FNIA01000003.1_167</t>
         </is>
       </c>
       <c r="L140" t="n">
-        <v>332</v>
+        <v>247</v>
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>ALAD</t>
+          <t>adh_short + KR + adh_short_C2</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>IH933_10425</t>
+          <t>BLT27_RS03620</t>
         </is>
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>MCH7660963.1</t>
+          <t>WP_089731670.1</t>
         </is>
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>porphobilinogen synthase</t>
+          <t>3-oxoacyl-ACP reductase FabG</t>
         </is>
       </c>
     </row>
@@ -18557,35 +18557,35 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Halalkalicoccus sp022561895</t>
+          <t>Haloarchaeobius iranensis</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>GCA_022561895.1</t>
+          <t>GCF_900103505.1</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>GenBank</t>
+          <t>RefSeq</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>-1</v>
+        <v>-5</v>
       </c>
       <c r="F141" t="b">
         <v>0</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>JADFQH010000144.1</t>
+          <t>NZ_FNIA01000003.1</t>
         </is>
       </c>
       <c r="H141" t="n">
-        <v>1435</v>
+        <v>154797</v>
       </c>
       <c r="I141" t="n">
-        <v>1878</v>
+        <v>156176</v>
       </c>
       <c r="J141" t="inlineStr">
         <is>
@@ -18594,30 +18594,30 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>JADFQH010000144.1_3</t>
+          <t>NZ_FNIA01000003.1_166</t>
         </is>
       </c>
       <c r="L141" t="n">
-        <v>147</v>
+        <v>459</v>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>LDcluster4</t>
+          <t>PhaC_N + Abhydrolase_1 + DUF3141 + HHH_5</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>IH933_10430</t>
+          <t>BLT27_RS03615</t>
         </is>
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t>MCH7660964.1</t>
+          <t>WP_089731669.1</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>TIGR00725 family protein</t>
+          <t>class III poly(R)-hydroxyalkanoic acid synthase subunit PhaC</t>
         </is>
       </c>
     </row>
@@ -18627,35 +18627,35 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Halalkalicoccus sp022561895</t>
+          <t>Haloarchaeobius iranensis</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>GCA_022561895.1</t>
+          <t>GCF_900103505.1</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>GenBank</t>
+          <t>RefSeq</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="F142" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>JADFQH010000144.1</t>
+          <t>NZ_FNIA01000003.1</t>
         </is>
       </c>
       <c r="H142" t="n">
-        <v>1965</v>
+        <v>154241</v>
       </c>
       <c r="I142" t="n">
-        <v>2843</v>
+        <v>154795</v>
       </c>
       <c r="J142" t="inlineStr">
         <is>
@@ -18664,26 +18664,26 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>JADFQH010000144.1_4</t>
+          <t>NZ_FNIA01000003.1_165</t>
         </is>
       </c>
       <c r="L142" t="n">
-        <v>292</v>
+        <v>184</v>
       </c>
       <c r="M142" t="inlineStr"/>
       <c r="N142" t="inlineStr">
         <is>
-          <t>IH933_10435</t>
+          <t>BLT27_RS03610</t>
         </is>
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>MCH7660965.1</t>
+          <t>WP_089731668.1</t>
         </is>
       </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>alpha/beta hydrolase</t>
+          <t>poly(R)-hydroxyalkanoic acid synthase subunit</t>
         </is>
       </c>
     </row>
@@ -18693,58 +18693,58 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Halalkalicoccus sp022561895</t>
+          <t>Haloarchaeobius iranensis</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>GCA_022561895.1</t>
+          <t>GCF_900103505.1</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>GenBank</t>
+          <t>RefSeq</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="F143" t="b">
         <v>0</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>JADFQH010000144.1</t>
+          <t>NZ_FNIA01000003.1</t>
         </is>
       </c>
       <c r="H143" t="n">
-        <v>3107</v>
+        <v>153706</v>
       </c>
       <c r="I143" t="n">
-        <v>3523</v>
+        <v>154194</v>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>JADFQH010000144.1_5</t>
+          <t>NZ_FNIA01000003.1_164</t>
         </is>
       </c>
       <c r="L143" t="n">
-        <v>138</v>
+        <v>162</v>
       </c>
       <c r="M143" t="inlineStr"/>
       <c r="N143" t="inlineStr">
         <is>
-          <t>IH933_10440</t>
+          <t>BLT27_RS03605</t>
         </is>
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t>MCH7660966.1</t>
+          <t>WP_089731667.1</t>
         </is>
       </c>
       <c r="P143" t="inlineStr">
@@ -18759,57 +18759,63 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Halalkalicoccus sp022561895</t>
+          <t>Haloarchaeobius iranensis</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>GCA_022561895.1</t>
+          <t>GCF_900103505.1</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>GenBank</t>
+          <t>RefSeq</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="F144" t="b">
         <v>0</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>JADFQH010000144.1</t>
+          <t>NZ_FNIA01000003.1</t>
         </is>
       </c>
       <c r="H144" t="n">
-        <v>3861</v>
+        <v>153387</v>
       </c>
       <c r="I144" t="n">
-        <v>4382</v>
+        <v>153713</v>
       </c>
       <c r="J144" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
-      <c r="L144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>NZ_FNIA01000003.1_163</t>
+        </is>
+      </c>
+      <c r="L144" t="n">
+        <v>108</v>
+      </c>
       <c r="M144" t="inlineStr"/>
       <c r="N144" t="inlineStr">
         <is>
-          <t>IH933_10445</t>
+          <t>BLT27_RS03600</t>
         </is>
       </c>
       <c r="O144" t="inlineStr">
         <is>
-          <t>MCH7660967.1</t>
+          <t>WP_089731666.1</t>
         </is>
       </c>
       <c r="P144" t="inlineStr">
         <is>
-          <t>hypothetical protein</t>
+          <t>AbrB/MazE/SpoVT family DNA-binding domain-containing protein</t>
         </is>
       </c>
     </row>
@@ -18819,35 +18825,35 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Halalkalicoccus sp022561895</t>
+          <t>Haloarchaeobius iranensis</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>GCA_022561895.1</t>
+          <t>GCF_900103505.1</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>GenBank</t>
+          <t>RefSeq</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="F145" t="b">
         <v>0</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>JADFQH010000144.1</t>
+          <t>NZ_FNIA01000003.1</t>
         </is>
       </c>
       <c r="H145" t="n">
-        <v>4391</v>
+        <v>152507</v>
       </c>
       <c r="I145" t="n">
-        <v>6514</v>
+        <v>153169</v>
       </c>
       <c r="J145" t="inlineStr">
         <is>
@@ -18856,30 +18862,30 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>JADFQH010000144.1_6</t>
+          <t>NZ_FNIA01000003.1_162</t>
         </is>
       </c>
       <c r="L145" t="n">
-        <v>707</v>
+        <v>220</v>
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Fer4_10 + Fer4 + Fer4_8 + Fer4_9 + CCG</t>
+          <t>MaoC_dehydratas + MaoC_dehydrat_N</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>IH933_10450</t>
+          <t>BLT27_RS03595</t>
         </is>
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t>MCH7660968.1</t>
+          <t>WP_368086022.1</t>
         </is>
       </c>
       <c r="P145" t="inlineStr">
         <is>
-          <t>4Fe-4S dicluster domain-containing protein</t>
+          <t>MaoC family dehydratase</t>
         </is>
       </c>
     </row>
@@ -18889,63 +18895,347 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Halalkalicoccus sp022561895</t>
+          <t>Haloarchaeobius iranensis</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>GCA_022561895.1</t>
+          <t>GCF_900103505.1</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>GenBank</t>
+          <t>RefSeq</t>
         </is>
       </c>
       <c r="E146" t="n">
+        <v>0</v>
+      </c>
+      <c r="F146" t="b">
+        <v>1</v>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>NZ_FNIA01000003.1</t>
+        </is>
+      </c>
+      <c r="H146" t="n">
+        <v>151461</v>
+      </c>
+      <c r="I146" t="n">
+        <v>152351</v>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>NZ_FNIA01000003.1_161</t>
+        </is>
+      </c>
+      <c r="L146" t="n">
+        <v>296</v>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>DUF900 + DUF726</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>BLT27_RS03590</t>
+        </is>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>WP_089731664.1</t>
+        </is>
+      </c>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>DUF726 domain-containing protein</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>10</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Haloarchaeobius iranensis</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>GCF_900103505.1</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>RefSeq</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>1</v>
+      </c>
+      <c r="F147" t="b">
+        <v>0</v>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>NZ_FNIA01000003.1</t>
+        </is>
+      </c>
+      <c r="H147" t="n">
+        <v>150119</v>
+      </c>
+      <c r="I147" t="n">
+        <v>151342</v>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>NZ_FNIA01000003.1_160</t>
+        </is>
+      </c>
+      <c r="L147" t="n">
+        <v>407</v>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>RGP</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>BLT27_RS03585</t>
+        </is>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>WP_089731663.1</t>
+        </is>
+      </c>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>alpha-1 4-glucan-protein synthase</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>10</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Haloarchaeobius iranensis</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>GCF_900103505.1</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>RefSeq</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>2</v>
+      </c>
+      <c r="F148" t="b">
+        <v>0</v>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>NZ_FNIA01000003.1</t>
+        </is>
+      </c>
+      <c r="H148" t="n">
+        <v>148928</v>
+      </c>
+      <c r="I148" t="n">
+        <v>150073</v>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>NZ_FNIA01000003.1_159</t>
+        </is>
+      </c>
+      <c r="L148" t="n">
+        <v>381</v>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>SBP_bac_11 + SBP_bac_8 + SBP_bac_6</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>BLT27_RS03580</t>
+        </is>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>WP_089731662.1</t>
+        </is>
+      </c>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>extracellular solute-binding protein</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>10</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Haloarchaeobius iranensis</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>GCF_900103505.1</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>RefSeq</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>3</v>
+      </c>
+      <c r="F149" t="b">
+        <v>0</v>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>NZ_FNIA01000003.1</t>
+        </is>
+      </c>
+      <c r="H149" t="n">
+        <v>147290</v>
+      </c>
+      <c r="I149" t="n">
+        <v>148924</v>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>NZ_FNIA01000003.1_158</t>
+        </is>
+      </c>
+      <c r="L149" t="n">
+        <v>544</v>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>BPD_transp_1 + BPD_transp_1</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>BLT27_RS03575</t>
+        </is>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>WP_089731661.1</t>
+        </is>
+      </c>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>ABC transporter permease</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>10</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Haloarchaeobius iranensis</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>GCF_900103505.1</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>RefSeq</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
         <v>4</v>
       </c>
-      <c r="F146" t="b">
-        <v>0</v>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>JADFQH010000144.1</t>
-        </is>
-      </c>
-      <c r="H146" t="n">
-        <v>7068</v>
-      </c>
-      <c r="I146" t="n">
-        <v>7412</v>
-      </c>
-      <c r="J146" t="inlineStr">
-        <is>
-          <t>+</t>
-        </is>
-      </c>
-      <c r="K146" t="inlineStr">
-        <is>
-          <t>JADFQH010000144.1_7</t>
-        </is>
-      </c>
-      <c r="L146" t="n">
-        <v>115</v>
-      </c>
-      <c r="M146" t="inlineStr"/>
-      <c r="N146" t="inlineStr">
-        <is>
-          <t>IH933_10455</t>
-        </is>
-      </c>
-      <c r="O146" t="inlineStr">
-        <is>
-          <t>MCH7660969.1</t>
-        </is>
-      </c>
-      <c r="P146" t="inlineStr">
-        <is>
-          <t>hypothetical protein</t>
+      <c r="F150" t="b">
+        <v>0</v>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>NZ_FNIA01000003.1</t>
+        </is>
+      </c>
+      <c r="H150" t="n">
+        <v>146149</v>
+      </c>
+      <c r="I150" t="n">
+        <v>147300</v>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>NZ_FNIA01000003.1_157</t>
+        </is>
+      </c>
+      <c r="L150" t="n">
+        <v>383</v>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>ABC_tran + TOBE_2</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>BLT27_RS03570</t>
+        </is>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>WP_089731660.1</t>
+        </is>
+      </c>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>ABC transporter ATP-binding protein</t>
         </is>
       </c>
     </row>
